--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.2.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.2.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18750610/oocihm.N_00155_18750610.2.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y133"/>
+  <dimension ref="A1:Y65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18750610\oocihm.N_00155_18750610.2.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L247: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: crimination â€” a knowledge of all that applies</t>
+          <t>L65: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: ssailed he ean reply ； his friends can meet</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L21: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The Hon. Edward Blakeâ€™s address to bis</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L28: isolated marker/symbol line :: ,</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -644,7 +648,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L464: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: you donâ€™t..</t>
+          <t>L464: punctuation artifact: repeated periods :: you don’t..</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -706,7 +710,7 @@
       </c>
       <c r="H3" s="1" t="inlineStr">
         <is>
-          <t>L283: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): CUlTIVatORS (odd internal casing) :: WEEDS.â€” A PRACTICAL HINT.- CUlTIVatORS</t>
+          <t>L283: suspicious token(s): CUlTIVatORS (odd internal casing) :: WEEDS.— A PRACTICAL HINT.- CUlTIVatORS</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
@@ -716,12 +720,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L254: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: eral, good soil â€” that is, well balanced, drained</t>
+          <t>L127: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS :: (a.） The room is comfortably cool, and the</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L24: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” consolation to the Opposition organs. They</t>
+          <t>L166: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: The •mbra Murder.</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -749,7 +753,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L1007: line starts with punctuation glued to text :: .about their opinions. For a comparatively</t>
+          <t>L410: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • He earns his bread with honest labor.</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -806,24 +810,24 @@
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>L1914: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 4Evening (letter/digit mix) :: " Houses and Housekeepingâ€� in 4Evening</t>
+          <t>L1914: suspicious token(s): 4Evening (letter/digit mix) :: " Houses and Housekeeping” in 4Evening</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L270: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: is accomplished. T Ï� come right to the point</t>
+          <t>L129: stray/suspicious non-ASCII glyph(s): U+FF09 FULLWIDTH RIGHT PARENTHESIS :: (b.）There is nothing tight about the neck;</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L27: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: graphs insteadâ€”paragraphs, however, which</t>
+          <t>L410: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • He earns his bread with honest labor.</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L240: isolated marker/symbol line :: V</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -833,7 +837,7 @@
       </c>
       <c r="P4" s="1" t="inlineStr">
         <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: â€œOh, yes, gimme 10 centsâ€™ wort of ha'r--</t>
+          <t>L467: punctuation artifact: double/multiple hyphen :: “Oh, yes, gimme 10 cents’ wort of ha'r--</t>
         </is>
       </c>
       <c r="Q4" s="1" t="inlineStr">
@@ -844,7 +848,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L2009: line starts with digit/letter garbage token | suspicious token(s): 1of (letter/digit mix) :: 1of the evidence. And the climax was added</t>
+          <t>L1007: line starts with punctuation glued to text :: .about their opinions. For a comparatively</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -874,12 +878,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>114</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -892,7 +896,7 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr">
         <is>
-          <t>L704: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): disturbingquestions (very long joined token) :: still,â€� The " disturbingquestions first</t>
+          <t>L704: suspicious token(s): disturbingquestions (very long joined token) :: still,” The " disturbingquestions first</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
@@ -902,19 +906,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L283: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): CUlTIVatORS (odd internal casing) :: WEEDS.â€” A PRACTICAL HINT.- CUlTIVatORS</t>
+          <t>L150: stray/suspicious non-ASCII glyph(s): U+4E4B CJK UNIFIED IDEOGRAPH-4E4B | isolated marker/symbol line :: 之</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L44: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: speech has been deliveredâ€”characterised,</t>
+          <t>L1731: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • It is reported in Montreal that the Grand</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L241: isolated marker/symbol line :: 2</t>
+          <t>L240: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -933,7 +937,11 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L1731: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • It is reported in Montreal that the Grand</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr">
         <is>
@@ -989,19 +997,19 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L309: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: weeks are from three to six inches highâ€”â€”</t>
+          <t>L482: stray/suspicious non-ASCII glyph(s): U+8DCC CJK UNIFIED IDEOGRAPH-8DCC | isolated marker/symbol line :: 跌</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L71: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: (e.) The light does not e nÃ© from in front!</t>
+          <t>L2336: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Arab and two-thirds of English blood—and</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L437: isolated marker/symbol line :: 0</t>
+          <t>L241: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -1020,7 +1028,11 @@
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L2009: line starts with digit/letter garbage token | suspicious token(s): 1of (letter/digit mix) :: 1of the evidence. And the climax was added</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr">
         <is>
@@ -1060,7 +1072,7 @@
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>L451: candidate OCR token mismatch vs other OCR: "noyed" vs "noted" :: noyed by children who have been in the habit</t>
+          <t>L648: candidate OCR token mismatch vs other OCR: "esire" vs "desire" :: left hand," madam, I esire to call your at-</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr"/>
@@ -1072,19 +1084,19 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: the window." " Boo-hoo-hoo!â€� said the little</t>
+          <t>L571: stray/suspicious non-ASCII glyph(s): U+8EAB CJK UNIFIED IDEOGRAPH-8EAB | isolated marker/symbol line :: 身</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L113: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: If you have to hold the pages of Harperâ€™s</t>
+          <t>L2437: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ¥</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L438: isolated marker/symbol line :: Q</t>
+          <t>L437: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
@@ -1103,7 +1115,11 @@
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L2336: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Arab and two-thirds of English blood—and</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr">
         <is>
@@ -1131,7 +1147,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -1143,31 +1159,31 @@
       <c r="E8" s="1" t="inlineStr"/>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>L473: candidate OCR token mismatch vs other OCR: "film" vs "flim" :: wanting some film-flam thing, and I</t>
+          <t>L708: candidate OCR token mismatch vs other OCR: "publie" vs "public" :: subjects intelligent publie discussion, and,</t>
         </is>
       </c>
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr">
         <is>
-          <t>L1063: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): wilfulmurderagainst (very long joined token) :: verdict of â€œwilfulmurderagainst</t>
+          <t>L1063: suspicious token(s): wilfulmurderagainst (very long joined token) :: verdict of “wilfulmurderagainst</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L466: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing matches been in vain.â€” Pr. Deu.</t>
+          <t>L576: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: The â€¢mbra Murder.</t>
+          <t>L2439: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L444: isolated marker/symbol line :: 4</t>
+          <t>L438: isolated marker/symbol line :: Q</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1222,31 +1238,31 @@
       <c r="E9" s="1" t="inlineStr"/>
       <c r="F9" s="1" t="inlineStr">
         <is>
-          <t>L648: candidate OCR token mismatch vs other OCR: "esire" vs "desire" :: left hand," madam, I esire to call your at-</t>
+          <t>L738: candidate OCR token mismatch vs other OCR: "victima" vs "victims" :: they are ever the victima of any such noble</t>
         </is>
       </c>
       <c r="G9" s="1" t="inlineStr"/>
       <c r="H9" s="1" t="inlineStr">
         <is>
-          <t>L1092: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): GiANTS (odd internal casing) :: OLD TIME GiANTS.â€” An English corre</t>
+          <t>L1092: suspicious token(s): GiANTS (odd internal casing) :: OLD TIME GiANTS.— An English corre</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: â€œOh, yes, gimme 10 centsâ€™ wort of ha'r--</t>
+          <t>L640: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: " No, madame ； I deal directly with the</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L196: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the cause of the poor manâ€™s death. A post</t>
+          <t>L2443: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L496: isolated marker/symbol line :: 2</t>
+          <t>L444: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1285,19 +1301,19 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
       <c r="E10" s="1" t="inlineStr"/>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>L708: candidate OCR token mismatch vs other OCR: "publie" vs "public" :: subjects intelligent publie discussion, and,</t>
+          <t>L968: candidate OCR token mismatch vs other OCR: "fcremost" vs "foremost" :: field, Ohio, stands fcremost at the present</t>
         </is>
       </c>
       <c r="G10" s="1" t="inlineStr"/>
@@ -1309,19 +1325,15 @@
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: " Do Ã© s he keep his bed Of course he</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L274: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: This "* Finlay horrorâ€� has created intense</t>
-        </is>
-      </c>
+          <t>L1069: stray/suspicious non-ASCII glyph(s): U+5C71 CJK UNIFIED IDEOGRAPH-5C71 | isolated marker/symbol line :: 山</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L497: isolated marker/symbol line :: 0</t>
+          <t>L482: stray/suspicious non-ASCII glyph(s): U+8DCC CJK UNIFIED IDEOGRAPH-8DCC | isolated marker/symbol line :: 跌</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1361,14 +1373,14 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr"/>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>L738: candidate OCR token mismatch vs other OCR: "victima" vs "victims" :: they are ever the victima of any such noble</t>
+          <t>L1194: candidate OCR token mismatch vs other OCR: "hooke" vs "hooked" :: they are hooke the fun begins in earnest.</t>
         </is>
       </c>
       <c r="G11" s="1" t="inlineStr"/>
@@ -1380,19 +1392,15 @@
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L704: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): disturbingquestions (very long joined token) :: still,â€� The " disturbingquestions first</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: make the confession she did.â€”Samia Ob-</t>
-        </is>
-      </c>
+          <t>L1236: stray/suspicious non-ASCII glyph(s): U+4E86 CJK UNIFIED IDEOGRAPH-4E86 | isolated marker/symbol line :: 了</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L572: isolated marker/symbol line :: 4</t>
+          <t>L496: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1423,7 +1431,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1435,31 +1443,27 @@
       <c r="E12" s="1" t="inlineStr"/>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>L968: candidate OCR token mismatch vs other OCR: "fcremost" vs "foremost" :: field, Ohio, stands fcremost at the present</t>
+          <t>L1321: candidate OCR token mismatch vs other OCR: "raisin" vs "raising" :: barn raisin at Mr. Thomas Cowan's, in the</t>
         </is>
       </c>
       <c r="G12" s="1" t="inlineStr"/>
       <c r="H12" s="1" t="inlineStr">
         <is>
-          <t>L1770: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): PreserVe (odd internal casing), frOm (odd internal casing) :: INFORMAL PEOPLE.â€” PreserVe uS frOm</t>
+          <t>L1770: suspicious token(s): PreserVe (odd internal casing), frOm (odd internal casing) :: INFORMAL PEOPLE.— PreserVe uS frOm</t>
         </is>
       </c>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L729: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " Canada correspondent of the â€” does not</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L341: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WEEDS.â€”A PRACTICAL HINT.â€”Cultivators</t>
-        </is>
-      </c>
+          <t>L1393: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK :: " J-a-w-n ！ J-a-w-n!” she shouted out of</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L637: isolated marker/symbol line :: m</t>
+          <t>L497: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1502,7 +1506,7 @@
       <c r="E13" s="1" t="inlineStr"/>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>L1194: candidate OCR token mismatch vs other OCR: "hooke" vs "hooked" :: they are hooke the fun begins in earnest.</t>
+          <t>L1342: suspicious token(s): AQGA2OADOOAOUAS (letter/digit mix) | localized OCR phrase divergence vs other OCR: "AQGA2OADOOAOUAS" vs "" :: AQGA2OADOOAOUAS</t>
         </is>
       </c>
       <c r="G13" s="1" t="inlineStr"/>
@@ -1514,19 +1518,15 @@
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L861: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: AN ENAMELLED CEING.â€”. ThE London</t>
-        </is>
-      </c>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L392: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Tis not the blood of kith and kin,</t>
-        </is>
-      </c>
+          <t>L1403: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB :: 1 享</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L652: isolated marker/symbol line :: 9</t>
+          <t>L571: stray/suspicious non-ASCII glyph(s): U+8EAB CJK UNIFIED IDEOGRAPH-8EAB | isolated marker/symbol line :: 身</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1562,16 +1562,12 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
       <c r="E14" s="1" t="inlineStr"/>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>L1321: candidate OCR token mismatch vs other OCR: "raisin" vs "raising" :: barn raisin at Mr. Thomas Cowan's, in the</t>
-        </is>
-      </c>
+      <c r="F14" s="1" t="inlineStr"/>
       <c r="G14" s="1" t="inlineStr"/>
       <c r="H14" s="1" t="inlineStr">
         <is>
@@ -1581,19 +1577,15 @@
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L892: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: quired â€” and the full heat of the summer, to</t>
-        </is>
-      </c>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L394: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Tis not the color of the skin;</t>
-        </is>
-      </c>
+          <t>L1435: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！”</t>
+        </is>
+      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L653: isolated marker/symbol line :: 4</t>
+          <t>L572: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1630,29 +1622,21 @@
       </c>
       <c r="D15" s="1" t="inlineStr"/>
       <c r="E15" s="1" t="inlineStr"/>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>L1342: suspicious token(s): AQGA2OADOOAOUAS (letter/digit mix) | localized OCR phrase divergence vs other OCR: "AQGA2OADOOAOUAS" vs "" :: AQGA2OADOOAOUAS</t>
-        </is>
-      </c>
+      <c r="F15" s="1" t="inlineStr"/>
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: ã€� The</t>
-        </is>
-      </c>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L396: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Tis the heart that beats within.</t>
-        </is>
-      </c>
+          <t>L1436: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK :: " You r-r-rascal ！ you villyun I” she</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L654: isolated marker/symbol line :: 4</t>
+          <t>L576: stray/suspicious non-ASCII glyph(s): U+4EAB CJK UNIFIED IDEOGRAPH-4EAB | isolated marker/symbol line :: 享</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1693,26 +1677,18 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L1031: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: does among showmenâ€”minus Barnum's hum-</t>
-        </is>
-      </c>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L410: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ He earns his bread with honest labor.</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L773: isolated marker/symbol line :: 2</t>
+          <t>L637: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L2437: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: Â¥</t>
+          <t>L2437: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ¥</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1748,26 +1724,18 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L1063: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): wilfulmurderagainst (very long joined token) :: verdict of â€œwilfulmurderagainst</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Of dreaming Jacobâ€™s starry ladder./</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L1069: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN | isolated marker/symbol line :: å±±</t>
+          <t>L652: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L2439: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L2439: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1791,21 +1759,13 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L1069: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN | isolated marker/symbol line :: å±±</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L421: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: And farther from the tempterâ€™s sway.</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L1070: isolated marker/symbol line :: 4</t>
+          <t>L653: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1834,26 +1794,18 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L1092: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): GiANTS (odd internal casing) :: OLD TIME GiANTS.â€” An English corre</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L444: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: And ills, like bats and owls, take flightâ€”</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L1230: isolated marker/symbol line :: 0</t>
+          <t>L654: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L2443: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L2443: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1877,21 +1829,13 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L1353: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: "What do you mean, sir?â€�she demanded,</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L446: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Heâ€™s greater than great Alexander.</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L1232: isolated marker/symbol line :: 2</t>
+          <t>L773: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -1920,21 +1864,13 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L1360: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " I want you to leave the house!â€� she</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L464: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: you donâ€™t..</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L1235: isolated marker/symbol line :: 2</t>
+          <t>L1069: stray/suspicious non-ASCII glyph(s): U+5C71 CJK UNIFIED IDEOGRAPH-5C71 | isolated marker/symbol line :: 山</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -1963,21 +1899,13 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L1365: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L467: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: discarding it forever, but he wasnâ€™t mourning</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L1239: isolated marker/symbol line :: 2</t>
+          <t>L1070: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -2006,21 +1934,13 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L1387: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " Get out Iâ€� she screamed; get out, or</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L475: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tion we have seen for a long time. It isnâ€™t</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L1246: isolated marker/symbol line :: 0</t>
+          <t>L1230: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -2049,21 +1969,13 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L1391: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: _â€�</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L476: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: an eye for an eyeâ€”but itâ€™s a leg for an arm.</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L1277: isolated marker/symbol line :: .</t>
+          <t>L1232: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2092,21 +2004,13 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L1393: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+20AC EURO SIGN :: " J-a-w-n ï¼� J-a-w-n!â€� she shouted out of</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L496: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ing matches been in vain.â€”Pr. Dev.]</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L1339: isolated marker/symbol line :: A</t>
+          <t>L1235: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2135,21 +2039,13 @@
       <c r="G26" s="1" t="inlineStr"/>
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
-      <c r="J26" s="1" t="inlineStr">
-        <is>
-          <t>L1435: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+20AC EURO SIGN :: ï¼�â€�</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L498: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " Oh, yes, gimme 10 centsâ€™ wort of haâ€™r-</t>
-        </is>
-      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L1340: isolated marker/symbol line :: 2</t>
+          <t>L1236: stray/suspicious non-ASCII glyph(s): U+4E86 CJK UNIFIED IDEOGRAPH-4E86 | isolated marker/symbol line :: 了</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -2174,21 +2070,13 @@
       <c r="G27" s="1" t="inlineStr"/>
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
-      <c r="J27" s="1" t="inlineStr">
-        <is>
-          <t>L1436: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+20AC EURO SIGN :: " You r-r-rascal ï¼� you villyun Iâ€� she</t>
-        </is>
-      </c>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L499: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: pins,â€� added a farmer, as he was about to</t>
-        </is>
-      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L1351: isolated marker/symbol line :: -</t>
+          <t>L1239: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -2213,21 +2101,13 @@
       <c r="G28" s="1" t="inlineStr"/>
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
-      <c r="J28" s="1" t="inlineStr">
-        <is>
-          <t>L1441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
-        </is>
-      </c>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L501: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: handed down, he continued: " Itâ€™s haâ€™r-</t>
-        </is>
-      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L1358: isolated marker/symbol line :: 1</t>
+          <t>L1246: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -2252,21 +2132,13 @@
       <c r="G29" s="1" t="inlineStr"/>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
-      <c r="J29" s="1" t="inlineStr">
-        <is>
-          <t>L1461: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " I vhants no bins or needles to-day!â€� she</t>
-        </is>
-      </c>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: shouldnâ€™t be surprised if sheâ€™d some day</t>
-        </is>
-      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L1359: isolated marker/symbol line :: 17</t>
+          <t>L1277: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -2291,21 +2163,13 @@
       <c r="G30" s="1" t="inlineStr"/>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>L1498: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: is asked for the disturbingâ€� Reformers of</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L513: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: man, with the old question : â€œ Howâ€™s Mr.</t>
-        </is>
-      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L1362: isolated marker/symbol line :: 2</t>
+          <t>L1339: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -2330,21 +2194,13 @@
       <c r="G31" s="1" t="inlineStr"/>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
-      <c r="J31" s="1" t="inlineStr">
-        <is>
-          <t>L1538: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œwealth, $40 or $50 was nothing to him."."."</t>
-        </is>
-      </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€”?â€� â€œSick,â€� replied the physician.</t>
-        </is>
-      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L1363: isolated marker/symbol line :: ,</t>
+          <t>L1340: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -2369,21 +2225,13 @@
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
-      <c r="J32" s="1" t="inlineStr">
-        <is>
-          <t>L1763: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: ti Å� n," whatsoever is get before you, eat, ask-</t>
-        </is>
-      </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L516: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: does. You donâ€™t suppose heâ€™s fool enough to</t>
-        </is>
-      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L1365: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L1351: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -2408,21 +2256,13 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
-      <c r="J33" s="1" t="inlineStr">
-        <is>
-          <t>L1770: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): PreserVe (odd internal casing), frOm (odd internal casing) :: INFORMAL PEOPLE.â€” PreserVe uS frOm</t>
-        </is>
-      </c>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L517: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sell his bed because heâ€™s sick, do you?"</t>
-        </is>
-      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L1366: isolated marker/symbol line :: 39</t>
+          <t>L1358: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -2447,21 +2287,13 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
-      <c r="J34" s="1" t="inlineStr">
-        <is>
-          <t>L1798: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: house to go hungry, my dear "â€” and any</t>
-        </is>
-      </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the other unfortunate, it is supposed.â€”Dan-</t>
-        </is>
-      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L1377: isolated marker/symbol line :: 39</t>
+          <t>L1359: isolated marker/symbol line :: 17</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -2486,21 +2318,13 @@
       <c r="G35" s="1" t="inlineStr"/>
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
-      <c r="J35" s="1" t="inlineStr">
-        <is>
-          <t>L1895: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” Welland Tribune.</t>
-        </is>
-      </c>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L529: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: FISHING.â€”An English writer says of fish-</t>
-        </is>
-      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L1392: symbol-only separator/garbage line :: _ 79</t>
+          <t>L1362: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -2525,21 +2349,13 @@
       <c r="G36" s="1" t="inlineStr"/>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
-      <c r="J36" s="1" t="inlineStr">
-        <is>
-          <t>L1978: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " Houses and Housekeepingâ€� in " Evening</t>
-        </is>
-      </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: tempted nothing.â€� Here the water comes</t>
-        </is>
-      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L1426: isolated marker/symbol line :: "</t>
+          <t>L1363: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -2564,21 +2380,13 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr">
-        <is>
-          <t>L2089: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: "I vhants no baper gollars Iâ€� she ex-</t>
-        </is>
-      </c>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: down in a rapidâ€™ rush, swirling round</t>
-        </is>
-      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L1427: isolated marker/symbol line :: 7</t>
+          <t>L1365: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2603,21 +2411,13 @@
       <c r="G38" s="1" t="inlineStr"/>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr">
-        <is>
-          <t>L2095: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
-        </is>
-      </c>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: criminationâ€”a knowledge of all that applies</t>
-        </is>
-      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L1434: isolated marker/symbol line :: !</t>
+          <t>L1366: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2642,21 +2442,13 @@
       <c r="G39" s="1" t="inlineStr"/>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr">
-        <is>
-          <t>L2096: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
-        </is>
-      </c>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L652: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: eral, good soilâ€”that is, well balanced, drained</t>
-        </is>
-      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L1440: isolated marker/symbol line :: U</t>
+          <t>L1377: isolated marker/symbol line :: 39</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2681,21 +2473,13 @@
       <c r="G40" s="1" t="inlineStr"/>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr">
-        <is>
-          <t>L2097: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " I vhants no matches â€” no dobacco-her â€” no</t>
-        </is>
-      </c>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L674: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: particular place in the seasonâ€”wheat to the</t>
-        </is>
-      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L1441: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L1391: isolated marker/symbol line :: _”</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2720,21 +2504,13 @@
       <c r="G41" s="1" t="inlineStr"/>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>L2098: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: zigars Iâ€� she interrupted; and her husband</t>
-        </is>
-      </c>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L687: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: benefit of the heat at the startâ€”which is re-</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="inlineStr"/>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L1442: isolated marker/symbol line :: , 3</t>
+          <t>L1392: symbol-only separator/garbage line :: _ 79</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2760,16 +2536,12 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L688: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: quiredâ€”and the full heat of the summer, to</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L1459: isolated marker/symbol line :: , 9</t>
+          <t>L1426: isolated marker/symbol line :: "</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2795,16 +2567,12 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: mer months and this is favorableâ€”a'general</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L1460: isolated marker/symbol line :: 99</t>
+          <t>L1427: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2830,16 +2598,12 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L725: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Thorough and deep drainageâ€”in other</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L1464: isolated marker/symbol line :: e</t>
+          <t>L1434: isolated marker/symbol line :: !</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2865,16 +2629,12 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: words, porosityâ€”will do this. A cellar is an</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L1465: isolated marker/symbol line :: 8</t>
+          <t>L1435: stray/suspicious non-ASCII glyph(s): U+FF01 FULLWIDTH EXCLAMATION MARK | isolated marker/symbol line :: ！”</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2900,16 +2660,12 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L741: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: are largely addedâ€”much more than is usually</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L1513: isolated marker/symbol line :: 1</t>
+          <t>L1440: isolated marker/symbol line :: U</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2935,16 +2691,12 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L774: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the better.â€”F. G. in the Country Gentleman.</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L1557: isolated marker/symbol line :: Â·</t>
+          <t>L1441: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2970,16 +2722,12 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L789: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: lion dollarsâ€™ worth of coral obtained last year</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L1572: isolated marker/symbol line :: ;</t>
+          <t>L1442: isolated marker/symbol line :: , 3</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -3005,16 +2753,12 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L900: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œThe Reform party in all portions of this,</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L1573: isolated marker/symbol line :: 4</t>
+          <t>L1459: isolated marker/symbol line :: , 9</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -3040,16 +2784,12 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L909: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The Peel election trial resumed at 9 oâ€™clock</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L1875: isolated marker/symbol line :: 2</t>
+          <t>L1460: isolated marker/symbol line :: 99</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -3075,16 +2815,12 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L913: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CANVASSING UNDER DISADVANTAGESâ€”THE PRO-</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L1876: isolated marker/symbol line :: e</t>
+          <t>L1464: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3110,16 +2846,12 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L915: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OF EXTERMINATIONâ€”A MATCH FOR AN AGENT.</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L1996: isolated marker/symbol line :: 0</t>
+          <t>L1465: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3145,16 +2877,12 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L952: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: me off the steps without glancing at it.â€�</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L2087: isolated marker/symbol line :: _ 9</t>
+          <t>L1513: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3180,16 +2908,12 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L954: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of Yourâ€”your what?" she asked.</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L2088: isolated marker/symbol line :: 92</t>
+          <t>L1557: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3215,16 +2939,12 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L956: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œ Madam,â€� he replied, as he placed a four-</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L2095: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L1572: isolated marker/symbol line :: ;</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3250,16 +2970,12 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L968: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: myâ€”â€”"</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L2096: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L1573: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3285,16 +3001,12 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œI will call the police !" she screamed,</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L2164: isolated marker/symbol line :: 1</t>
+          <t>L1875: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3320,16 +3032,12 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L986: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: factured at Oshava.â€”Immense Suc-</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L2175: isolated marker/symbol line :: C</t>
+          <t>L1876: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3355,14 +3063,14 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1053: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: world over. The electorateâ€”the peopleâ€”are</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
+      <c r="N59" s="1" t="inlineStr">
+        <is>
+          <t>L1996: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O59" s="1" t="inlineStr"/>
       <c r="P59" s="1" t="inlineStr"/>
       <c r="Q59" s="1" t="inlineStr"/>
@@ -3386,14 +3094,14 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1056: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: creature, their servantâ€”not their master ;</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
+      <c r="N60" s="1" t="inlineStr">
+        <is>
+          <t>L2087: isolated marker/symbol line :: _ 9</t>
+        </is>
+      </c>
       <c r="O60" s="1" t="inlineStr"/>
       <c r="P60" s="1" t="inlineStr"/>
       <c r="Q60" s="1" t="inlineStr"/>
@@ -3417,14 +3125,14 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1070: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: The " rest and be thankfulâ€� policy is not his</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
+      <c r="N61" s="1" t="inlineStr">
+        <is>
+          <t>L2088: isolated marker/symbol line :: 92</t>
+        </is>
+      </c>
       <c r="O61" s="1" t="inlineStr"/>
       <c r="P61" s="1" t="inlineStr"/>
       <c r="Q61" s="1" t="inlineStr"/>
@@ -3448,14 +3156,14 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1076: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: still.â€� The ** disturbing" questions first</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
-      <c r="N62" s="1" t="inlineStr"/>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>L2095: isolated marker/symbol line :: ”</t>
+        </is>
+      </c>
       <c r="O62" s="1" t="inlineStr"/>
       <c r="P62" s="1" t="inlineStr"/>
       <c r="Q62" s="1" t="inlineStr"/>
@@ -3479,14 +3187,14 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1089: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " federation of the Empire,â€� &amp;c., absurd</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
+      <c r="N63" s="1" t="inlineStr">
+        <is>
+          <t>L2096: isolated marker/symbol line :: ”</t>
+        </is>
+      </c>
       <c r="O63" s="1" t="inlineStr"/>
       <c r="P63" s="1" t="inlineStr"/>
       <c r="Q63" s="1" t="inlineStr"/>
@@ -3510,14 +3218,14 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1122: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6 Canada correspondent of the -â€” does not</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
+      <c r="N64" s="1" t="inlineStr">
+        <is>
+          <t>L2164: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="O64" s="1" t="inlineStr"/>
       <c r="P64" s="1" t="inlineStr"/>
       <c r="Q64" s="1" t="inlineStr"/>
@@ -3541,14 +3249,14 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1124: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜public have for some time bestowed on the</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
-      <c r="N65" s="1" t="inlineStr"/>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t>L2175: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
       <c r="O65" s="1" t="inlineStr"/>
       <c r="P65" s="1" t="inlineStr"/>
       <c r="Q65" s="1" t="inlineStr"/>
@@ -3561,2114 +3269,6 @@
       <c r="X65" s="1" t="inlineStr"/>
       <c r="Y65" s="1" t="inlineStr"/>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr"/>
-      <c r="B66" s="1" t="inlineStr"/>
-      <c r="C66" s="1" t="inlineStr"/>
-      <c r="D66" s="1" t="inlineStr"/>
-      <c r="E66" s="1" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: " paragraph;â€� â€œit is therefore pleasant to</t>
-        </is>
-      </c>
-      <c r="L66" s="1" t="inlineStr"/>
-      <c r="M66" s="1" t="inlineStr"/>
-      <c r="N66" s="1" t="inlineStr"/>
-      <c r="O66" s="1" t="inlineStr"/>
-      <c r="P66" s="1" t="inlineStr"/>
-      <c r="Q66" s="1" t="inlineStr"/>
-      <c r="R66" s="1" t="inlineStr"/>
-      <c r="S66" s="1" t="inlineStr"/>
-      <c r="T66" s="1" t="inlineStr"/>
-      <c r="U66" s="1" t="inlineStr"/>
-      <c r="V66" s="1" t="inlineStr"/>
-      <c r="W66" s="1" t="inlineStr"/>
-      <c r="X66" s="1" t="inlineStr"/>
-      <c r="Y66" s="1" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr"/>
-      <c r="B67" s="1" t="inlineStr"/>
-      <c r="C67" s="1" t="inlineStr"/>
-      <c r="D67" s="1" t="inlineStr"/>
-      <c r="E67" s="1" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: [From the Farmerâ€™s Advocate, June, 1875.]</t>
-        </is>
-      </c>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr"/>
-      <c r="R67" s="1" t="inlineStr"/>
-      <c r="S67" s="1" t="inlineStr"/>
-      <c r="T67" s="1" t="inlineStr"/>
-      <c r="U67" s="1" t="inlineStr"/>
-      <c r="V67" s="1" t="inlineStr"/>
-      <c r="W67" s="1" t="inlineStr"/>
-      <c r="X67" s="1" t="inlineStr"/>
-      <c r="Y67" s="1" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr"/>
-      <c r="B68" s="1" t="inlineStr"/>
-      <c r="C68" s="1" t="inlineStr"/>
-      <c r="D68" s="1" t="inlineStr"/>
-      <c r="E68" s="1" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1234: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: thereâ€”May 12thâ€”600 had been shipped, and</t>
-        </is>
-      </c>
-      <c r="L68" s="1" t="inlineStr"/>
-      <c r="M68" s="1" t="inlineStr"/>
-      <c r="N68" s="1" t="inlineStr"/>
-      <c r="O68" s="1" t="inlineStr"/>
-      <c r="P68" s="1" t="inlineStr"/>
-      <c r="Q68" s="1" t="inlineStr"/>
-      <c r="R68" s="1" t="inlineStr"/>
-      <c r="S68" s="1" t="inlineStr"/>
-      <c r="T68" s="1" t="inlineStr"/>
-      <c r="U68" s="1" t="inlineStr"/>
-      <c r="V68" s="1" t="inlineStr"/>
-      <c r="W68" s="1" t="inlineStr"/>
-      <c r="X68" s="1" t="inlineStr"/>
-      <c r="Y68" s="1" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr"/>
-      <c r="B69" s="1" t="inlineStr"/>
-      <c r="C69" s="1" t="inlineStr"/>
-      <c r="D69" s="1" t="inlineStr"/>
-      <c r="E69" s="1" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L1263: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: does among showmenâ€”minus Barnumâ€™s hum-</t>
-        </is>
-      </c>
-      <c r="L69" s="1" t="inlineStr"/>
-      <c r="M69" s="1" t="inlineStr"/>
-      <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr"/>
-      <c r="P69" s="1" t="inlineStr"/>
-      <c r="Q69" s="1" t="inlineStr"/>
-      <c r="R69" s="1" t="inlineStr"/>
-      <c r="S69" s="1" t="inlineStr"/>
-      <c r="T69" s="1" t="inlineStr"/>
-      <c r="U69" s="1" t="inlineStr"/>
-      <c r="V69" s="1" t="inlineStr"/>
-      <c r="W69" s="1" t="inlineStr"/>
-      <c r="X69" s="1" t="inlineStr"/>
-      <c r="Y69" s="1" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr"/>
-      <c r="B70" s="1" t="inlineStr"/>
-      <c r="C70" s="1" t="inlineStr"/>
-      <c r="D70" s="1" t="inlineStr"/>
-      <c r="E70" s="1" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L1276: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and six oâ€™clock the streets are almost black</t>
-        </is>
-      </c>
-      <c r="L70" s="1" t="inlineStr"/>
-      <c r="M70" s="1" t="inlineStr"/>
-      <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr"/>
-      <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr"/>
-      <c r="R70" s="1" t="inlineStr"/>
-      <c r="S70" s="1" t="inlineStr"/>
-      <c r="T70" s="1" t="inlineStr"/>
-      <c r="U70" s="1" t="inlineStr"/>
-      <c r="V70" s="1" t="inlineStr"/>
-      <c r="W70" s="1" t="inlineStr"/>
-      <c r="X70" s="1" t="inlineStr"/>
-      <c r="Y70" s="1" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr"/>
-      <c r="B71" s="1" t="inlineStr"/>
-      <c r="C71" s="1" t="inlineStr"/>
-      <c r="D71" s="1" t="inlineStr"/>
-      <c r="E71" s="1" t="inlineStr"/>
-      <c r="F71" s="1" t="inlineStr"/>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L1287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: â€œ Madam, I donâ€™t wish to</t>
-        </is>
-      </c>
-      <c r="L71" s="1" t="inlineStr"/>
-      <c r="M71" s="1" t="inlineStr"/>
-      <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr"/>
-      <c r="P71" s="1" t="inlineStr"/>
-      <c r="Q71" s="1" t="inlineStr"/>
-      <c r="R71" s="1" t="inlineStr"/>
-      <c r="S71" s="1" t="inlineStr"/>
-      <c r="T71" s="1" t="inlineStr"/>
-      <c r="U71" s="1" t="inlineStr"/>
-      <c r="V71" s="1" t="inlineStr"/>
-      <c r="W71" s="1" t="inlineStr"/>
-      <c r="X71" s="1" t="inlineStr"/>
-      <c r="Y71" s="1" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr"/>
-      <c r="B72" s="1" t="inlineStr"/>
-      <c r="C72" s="1" t="inlineStr"/>
-      <c r="D72" s="1" t="inlineStr"/>
-      <c r="E72" s="1" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr"/>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L1337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and saidâ€”</t>
-        </is>
-      </c>
-      <c r="L72" s="1" t="inlineStr"/>
-      <c r="M72" s="1" t="inlineStr"/>
-      <c r="N72" s="1" t="inlineStr"/>
-      <c r="O72" s="1" t="inlineStr"/>
-      <c r="P72" s="1" t="inlineStr"/>
-      <c r="Q72" s="1" t="inlineStr"/>
-      <c r="R72" s="1" t="inlineStr"/>
-      <c r="S72" s="1" t="inlineStr"/>
-      <c r="T72" s="1" t="inlineStr"/>
-      <c r="U72" s="1" t="inlineStr"/>
-      <c r="V72" s="1" t="inlineStr"/>
-      <c r="W72" s="1" t="inlineStr"/>
-      <c r="X72" s="1" t="inlineStr"/>
-      <c r="Y72" s="1" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr"/>
-      <c r="B73" s="1" t="inlineStr"/>
-      <c r="C73" s="1" t="inlineStr"/>
-      <c r="D73" s="1" t="inlineStr"/>
-      <c r="E73" s="1" t="inlineStr"/>
-      <c r="F73" s="1" t="inlineStr"/>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L1355: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: hance the comforts of the nightâ€”to produce</t>
-        </is>
-      </c>
-      <c r="L73" s="1" t="inlineStr"/>
-      <c r="M73" s="1" t="inlineStr"/>
-      <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr"/>
-      <c r="P73" s="1" t="inlineStr"/>
-      <c r="Q73" s="1" t="inlineStr"/>
-      <c r="R73" s="1" t="inlineStr"/>
-      <c r="S73" s="1" t="inlineStr"/>
-      <c r="T73" s="1" t="inlineStr"/>
-      <c r="U73" s="1" t="inlineStr"/>
-      <c r="V73" s="1" t="inlineStr"/>
-      <c r="W73" s="1" t="inlineStr"/>
-      <c r="X73" s="1" t="inlineStr"/>
-      <c r="Y73" s="1" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr"/>
-      <c r="B74" s="1" t="inlineStr"/>
-      <c r="C74" s="1" t="inlineStr"/>
-      <c r="D74" s="1" t="inlineStr"/>
-      <c r="E74" s="1" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L1366: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: royal palace of her Majesty Qâ€”â€” !".</t>
-        </is>
-      </c>
-      <c r="L74" s="1" t="inlineStr"/>
-      <c r="M74" s="1" t="inlineStr"/>
-      <c r="N74" s="1" t="inlineStr"/>
-      <c r="O74" s="1" t="inlineStr"/>
-      <c r="P74" s="1" t="inlineStr"/>
-      <c r="Q74" s="1" t="inlineStr"/>
-      <c r="R74" s="1" t="inlineStr"/>
-      <c r="S74" s="1" t="inlineStr"/>
-      <c r="T74" s="1" t="inlineStr"/>
-      <c r="U74" s="1" t="inlineStr"/>
-      <c r="V74" s="1" t="inlineStr"/>
-      <c r="W74" s="1" t="inlineStr"/>
-      <c r="X74" s="1" t="inlineStr"/>
-      <c r="Y74" s="1" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr"/>
-      <c r="B75" s="1" t="inlineStr"/>
-      <c r="C75" s="1" t="inlineStr"/>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L1386: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œ I vhants no zoap,â€� said the woman of</t>
-        </is>
-      </c>
-      <c r="L75" s="1" t="inlineStr"/>
-      <c r="M75" s="1" t="inlineStr"/>
-      <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr"/>
-      <c r="P75" s="1" t="inlineStr"/>
-      <c r="Q75" s="1" t="inlineStr"/>
-      <c r="R75" s="1" t="inlineStr"/>
-      <c r="S75" s="1" t="inlineStr"/>
-      <c r="T75" s="1" t="inlineStr"/>
-      <c r="U75" s="1" t="inlineStr"/>
-      <c r="V75" s="1" t="inlineStr"/>
-      <c r="W75" s="1" t="inlineStr"/>
-      <c r="X75" s="1" t="inlineStr"/>
-      <c r="Y75" s="1" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr"/>
-      <c r="B76" s="1" t="inlineStr"/>
-      <c r="C76" s="1" t="inlineStr"/>
-      <c r="D76" s="1" t="inlineStr"/>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L1392: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: festedâ€”"</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr"/>
-      <c r="M76" s="1" t="inlineStr"/>
-      <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr"/>
-      <c r="P76" s="1" t="inlineStr"/>
-      <c r="Q76" s="1" t="inlineStr"/>
-      <c r="R76" s="1" t="inlineStr"/>
-      <c r="S76" s="1" t="inlineStr"/>
-      <c r="T76" s="1" t="inlineStr"/>
-      <c r="U76" s="1" t="inlineStr"/>
-      <c r="V76" s="1" t="inlineStr"/>
-      <c r="W76" s="1" t="inlineStr"/>
-      <c r="X76" s="1" t="inlineStr"/>
-      <c r="Y76" s="1" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr"/>
-      <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" s="1" t="inlineStr"/>
-      <c r="D77" s="1" t="inlineStr"/>
-      <c r="E77" s="1" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L1397: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Madam, I am not a peddler of Yankee</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr"/>
-      <c r="M77" s="1" t="inlineStr"/>
-      <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr"/>
-      <c r="P77" s="1" t="inlineStr"/>
-      <c r="Q77" s="1" t="inlineStr"/>
-      <c r="R77" s="1" t="inlineStr"/>
-      <c r="S77" s="1" t="inlineStr"/>
-      <c r="T77" s="1" t="inlineStr"/>
-      <c r="U77" s="1" t="inlineStr"/>
-      <c r="V77" s="1" t="inlineStr"/>
-      <c r="W77" s="1" t="inlineStr"/>
-      <c r="X77" s="1" t="inlineStr"/>
-      <c r="Y77" s="1" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr"/>
-      <c r="B78" s="1" t="inlineStr"/>
-      <c r="C78" s="1" t="inlineStr"/>
-      <c r="D78" s="1" t="inlineStr"/>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1400: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ed to â€”"</t>
-        </is>
-      </c>
-      <c r="L78" s="1" t="inlineStr"/>
-      <c r="M78" s="1" t="inlineStr"/>
-      <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr"/>
-      <c r="P78" s="1" t="inlineStr"/>
-      <c r="Q78" s="1" t="inlineStr"/>
-      <c r="R78" s="1" t="inlineStr"/>
-      <c r="S78" s="1" t="inlineStr"/>
-      <c r="T78" s="1" t="inlineStr"/>
-      <c r="U78" s="1" t="inlineStr"/>
-      <c r="V78" s="1" t="inlineStr"/>
-      <c r="W78" s="1" t="inlineStr"/>
-      <c r="X78" s="1" t="inlineStr"/>
-      <c r="Y78" s="1" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr"/>
-      <c r="B79" s="1" t="inlineStr"/>
-      <c r="C79" s="1" t="inlineStr"/>
-      <c r="D79" s="1" t="inlineStr"/>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1408: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: unlock my trunk and showâ€”â€�</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr"/>
-      <c r="R79" s="1" t="inlineStr"/>
-      <c r="S79" s="1" t="inlineStr"/>
-      <c r="T79" s="1" t="inlineStr"/>
-      <c r="U79" s="1" t="inlineStr"/>
-      <c r="V79" s="1" t="inlineStr"/>
-      <c r="W79" s="1" t="inlineStr"/>
-      <c r="X79" s="1" t="inlineStr"/>
-      <c r="Y79" s="1" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="1" t="inlineStr"/>
-      <c r="C80" s="1" t="inlineStr"/>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L1410: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: " I vhants no matchesâ€”no dobaccoâ€”no</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" s="1" t="inlineStr"/>
-      <c r="Q80" s="1" t="inlineStr"/>
-      <c r="R80" s="1" t="inlineStr"/>
-      <c r="S80" s="1" t="inlineStr"/>
-      <c r="T80" s="1" t="inlineStr"/>
-      <c r="U80" s="1" t="inlineStr"/>
-      <c r="V80" s="1" t="inlineStr"/>
-      <c r="W80" s="1" t="inlineStr"/>
-      <c r="X80" s="1" t="inlineStr"/>
-      <c r="Y80" s="1" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr"/>
-      <c r="B81" s="1" t="inlineStr"/>
-      <c r="C81" s="1" t="inlineStr"/>
-      <c r="D81" s="1" t="inlineStr"/>
-      <c r="E81" s="1" t="inlineStr"/>
-      <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L1415: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " If you donâ€™t be quick out of here I shall</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr"/>
-      <c r="R81" s="1" t="inlineStr"/>
-      <c r="S81" s="1" t="inlineStr"/>
-      <c r="T81" s="1" t="inlineStr"/>
-      <c r="U81" s="1" t="inlineStr"/>
-      <c r="V81" s="1" t="inlineStr"/>
-      <c r="W81" s="1" t="inlineStr"/>
-      <c r="X81" s="1" t="inlineStr"/>
-      <c r="Y81" s="1" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr"/>
-      <c r="E82" s="1" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L1416: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: not have any shoking about it Iâ€�</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
-      <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr"/>
-      <c r="R82" s="1" t="inlineStr"/>
-      <c r="S82" s="1" t="inlineStr"/>
-      <c r="T82" s="1" t="inlineStr"/>
-      <c r="U82" s="1" t="inlineStr"/>
-      <c r="V82" s="1" t="inlineStr"/>
-      <c r="W82" s="1" t="inlineStr"/>
-      <c r="X82" s="1" t="inlineStr"/>
-      <c r="Y82" s="1" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="1" t="inlineStr"/>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L1424: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”The Czar will soon receive a magnificent</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr"/>
-      <c r="R83" s="1" t="inlineStr"/>
-      <c r="S83" s="1" t="inlineStr"/>
-      <c r="T83" s="1" t="inlineStr"/>
-      <c r="U83" s="1" t="inlineStr"/>
-      <c r="V83" s="1" t="inlineStr"/>
-      <c r="W83" s="1" t="inlineStr"/>
-      <c r="X83" s="1" t="inlineStr"/>
-      <c r="Y83" s="1" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr"/>
-      <c r="B84" s="1" t="inlineStr"/>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr"/>
-      <c r="E84" s="1" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L1474: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: An ENAMELLED CELLING.â€”The London</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
-      <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr"/>
-      <c r="R84" s="1" t="inlineStr"/>
-      <c r="S84" s="1" t="inlineStr"/>
-      <c r="T84" s="1" t="inlineStr"/>
-      <c r="U84" s="1" t="inlineStr"/>
-      <c r="V84" s="1" t="inlineStr"/>
-      <c r="W84" s="1" t="inlineStr"/>
-      <c r="X84" s="1" t="inlineStr"/>
-      <c r="Y84" s="1" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="1" t="inlineStr"/>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L1530: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Johnâ€™s credit in the historic judgment</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr"/>
-      <c r="R85" s="1" t="inlineStr"/>
-      <c r="S85" s="1" t="inlineStr"/>
-      <c r="T85" s="1" t="inlineStr"/>
-      <c r="U85" s="1" t="inlineStr"/>
-      <c r="V85" s="1" t="inlineStr"/>
-      <c r="W85" s="1" t="inlineStr"/>
-      <c r="X85" s="1" t="inlineStr"/>
-      <c r="Y85" s="1" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="1" t="inlineStr"/>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L1550: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: last general election was decisive.â€”The</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr"/>
-      <c r="R86" s="1" t="inlineStr"/>
-      <c r="S86" s="1" t="inlineStr"/>
-      <c r="T86" s="1" t="inlineStr"/>
-      <c r="U86" s="1" t="inlineStr"/>
-      <c r="V86" s="1" t="inlineStr"/>
-      <c r="W86" s="1" t="inlineStr"/>
-      <c r="X86" s="1" t="inlineStr"/>
-      <c r="Y86" s="1" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr"/>
-      <c r="B87" s="1" t="inlineStr"/>
-      <c r="C87" s="1" t="inlineStr"/>
-      <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L1588: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: 6* nice presentâ€� to an old woman. This he</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr"/>
-      <c r="R87" s="1" t="inlineStr"/>
-      <c r="S87" s="1" t="inlineStr"/>
-      <c r="T87" s="1" t="inlineStr"/>
-      <c r="U87" s="1" t="inlineStr"/>
-      <c r="V87" s="1" t="inlineStr"/>
-      <c r="W87" s="1" t="inlineStr"/>
-      <c r="X87" s="1" t="inlineStr"/>
-      <c r="Y87" s="1" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr"/>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L1619: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OLD TIME GIANTS.â€”An English corre-</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
-      <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr"/>
-      <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr"/>
-      <c r="R88" s="1" t="inlineStr"/>
-      <c r="S88" s="1" t="inlineStr"/>
-      <c r="T88" s="1" t="inlineStr"/>
-      <c r="U88" s="1" t="inlineStr"/>
-      <c r="V88" s="1" t="inlineStr"/>
-      <c r="W88" s="1" t="inlineStr"/>
-      <c r="X88" s="1" t="inlineStr"/>
-      <c r="Y88" s="1" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr"/>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
-      <c r="F89" s="1" t="inlineStr"/>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L1625: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lings." A late editor adds, â€œdoes this mean,</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr"/>
-      <c r="R89" s="1" t="inlineStr"/>
-      <c r="S89" s="1" t="inlineStr"/>
-      <c r="T89" s="1" t="inlineStr"/>
-      <c r="U89" s="1" t="inlineStr"/>
-      <c r="V89" s="1" t="inlineStr"/>
-      <c r="W89" s="1" t="inlineStr"/>
-      <c r="X89" s="1" t="inlineStr"/>
-      <c r="Y89" s="1" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="inlineStr"/>
-      <c r="B90" s="1" t="inlineStr"/>
-      <c r="C90" s="1" t="inlineStr"/>
-      <c r="D90" s="1" t="inlineStr"/>
-      <c r="E90" s="1" t="inlineStr"/>
-      <c r="F90" s="1" t="inlineStr"/>
-      <c r="G90" s="1" t="inlineStr"/>
-      <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
-      <c r="J90" s="1" t="inlineStr"/>
-      <c r="K90" s="1" t="inlineStr">
-        <is>
-          <t>L1626: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜slipped two shillings into the child's hand?'"</t>
-        </is>
-      </c>
-      <c r="L90" s="1" t="inlineStr"/>
-      <c r="M90" s="1" t="inlineStr"/>
-      <c r="N90" s="1" t="inlineStr"/>
-      <c r="O90" s="1" t="inlineStr"/>
-      <c r="P90" s="1" t="inlineStr"/>
-      <c r="Q90" s="1" t="inlineStr"/>
-      <c r="R90" s="1" t="inlineStr"/>
-      <c r="S90" s="1" t="inlineStr"/>
-      <c r="T90" s="1" t="inlineStr"/>
-      <c r="U90" s="1" t="inlineStr"/>
-      <c r="V90" s="1" t="inlineStr"/>
-      <c r="W90" s="1" t="inlineStr"/>
-      <c r="X90" s="1" t="inlineStr"/>
-      <c r="Y90" s="1" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr"/>
-      <c r="B91" s="1" t="inlineStr"/>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr"/>
-      <c r="E91" s="1" t="inlineStr"/>
-      <c r="F91" s="1" t="inlineStr"/>
-      <c r="G91" s="1" t="inlineStr"/>
-      <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr"/>
-      <c r="J91" s="1" t="inlineStr"/>
-      <c r="K91" s="1" t="inlineStr">
-        <is>
-          <t>L1665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: died about the time of Mr. Pepysâ€™s birth.</t>
-        </is>
-      </c>
-      <c r="L91" s="1" t="inlineStr"/>
-      <c r="M91" s="1" t="inlineStr"/>
-      <c r="N91" s="1" t="inlineStr"/>
-      <c r="O91" s="1" t="inlineStr"/>
-      <c r="P91" s="1" t="inlineStr"/>
-      <c r="Q91" s="1" t="inlineStr"/>
-      <c r="R91" s="1" t="inlineStr"/>
-      <c r="S91" s="1" t="inlineStr"/>
-      <c r="T91" s="1" t="inlineStr"/>
-      <c r="U91" s="1" t="inlineStr"/>
-      <c r="V91" s="1" t="inlineStr"/>
-      <c r="W91" s="1" t="inlineStr"/>
-      <c r="X91" s="1" t="inlineStr"/>
-      <c r="Y91" s="1" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="inlineStr"/>
-      <c r="B92" s="1" t="inlineStr"/>
-      <c r="C92" s="1" t="inlineStr"/>
-      <c r="D92" s="1" t="inlineStr"/>
-      <c r="E92" s="1" t="inlineStr"/>
-      <c r="F92" s="1" t="inlineStr"/>
-      <c r="G92" s="1" t="inlineStr"/>
-      <c r="H92" s="1" t="inlineStr"/>
-      <c r="I92" s="1" t="inlineStr"/>
-      <c r="J92" s="1" t="inlineStr"/>
-      <c r="K92" s="1" t="inlineStr">
-        <is>
-          <t>L1668: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: JURY.â€”The jury to inquire into the manner of</t>
-        </is>
-      </c>
-      <c r="L92" s="1" t="inlineStr"/>
-      <c r="M92" s="1" t="inlineStr"/>
-      <c r="N92" s="1" t="inlineStr"/>
-      <c r="O92" s="1" t="inlineStr"/>
-      <c r="P92" s="1" t="inlineStr"/>
-      <c r="Q92" s="1" t="inlineStr"/>
-      <c r="R92" s="1" t="inlineStr"/>
-      <c r="S92" s="1" t="inlineStr"/>
-      <c r="T92" s="1" t="inlineStr"/>
-      <c r="U92" s="1" t="inlineStr"/>
-      <c r="V92" s="1" t="inlineStr"/>
-      <c r="W92" s="1" t="inlineStr"/>
-      <c r="X92" s="1" t="inlineStr"/>
-      <c r="Y92" s="1" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr"/>
-      <c r="B93" s="1" t="inlineStr"/>
-      <c r="C93" s="1" t="inlineStr"/>
-      <c r="D93" s="1" t="inlineStr"/>
-      <c r="E93" s="1" t="inlineStr"/>
-      <c r="F93" s="1" t="inlineStr"/>
-      <c r="G93" s="1" t="inlineStr"/>
-      <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr"/>
-      <c r="J93" s="1" t="inlineStr"/>
-      <c r="K93" s="1" t="inlineStr">
-        <is>
-          <t>L1691: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: REFORM MEETING.â€”The members of the</t>
-        </is>
-      </c>
-      <c r="L93" s="1" t="inlineStr"/>
-      <c r="M93" s="1" t="inlineStr"/>
-      <c r="N93" s="1" t="inlineStr"/>
-      <c r="O93" s="1" t="inlineStr"/>
-      <c r="P93" s="1" t="inlineStr"/>
-      <c r="Q93" s="1" t="inlineStr"/>
-      <c r="R93" s="1" t="inlineStr"/>
-      <c r="S93" s="1" t="inlineStr"/>
-      <c r="T93" s="1" t="inlineStr"/>
-      <c r="U93" s="1" t="inlineStr"/>
-      <c r="V93" s="1" t="inlineStr"/>
-      <c r="W93" s="1" t="inlineStr"/>
-      <c r="X93" s="1" t="inlineStr"/>
-      <c r="Y93" s="1" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="inlineStr"/>
-      <c r="B94" s="1" t="inlineStr"/>
-      <c r="C94" s="1" t="inlineStr"/>
-      <c r="D94" s="1" t="inlineStr"/>
-      <c r="E94" s="1" t="inlineStr"/>
-      <c r="F94" s="1" t="inlineStr"/>
-      <c r="G94" s="1" t="inlineStr"/>
-      <c r="H94" s="1" t="inlineStr"/>
-      <c r="I94" s="1" t="inlineStr"/>
-      <c r="J94" s="1" t="inlineStr"/>
-      <c r="K94" s="1" t="inlineStr">
-        <is>
-          <t>L1731: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ It is reported in Montreal that the Grand</t>
-        </is>
-      </c>
-      <c r="L94" s="1" t="inlineStr"/>
-      <c r="M94" s="1" t="inlineStr"/>
-      <c r="N94" s="1" t="inlineStr"/>
-      <c r="O94" s="1" t="inlineStr"/>
-      <c r="P94" s="1" t="inlineStr"/>
-      <c r="Q94" s="1" t="inlineStr"/>
-      <c r="R94" s="1" t="inlineStr"/>
-      <c r="S94" s="1" t="inlineStr"/>
-      <c r="T94" s="1" t="inlineStr"/>
-      <c r="U94" s="1" t="inlineStr"/>
-      <c r="V94" s="1" t="inlineStr"/>
-      <c r="W94" s="1" t="inlineStr"/>
-      <c r="X94" s="1" t="inlineStr"/>
-      <c r="Y94" s="1" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="inlineStr"/>
-      <c r="B95" s="1" t="inlineStr"/>
-      <c r="C95" s="1" t="inlineStr"/>
-      <c r="D95" s="1" t="inlineStr"/>
-      <c r="E95" s="1" t="inlineStr"/>
-      <c r="F95" s="1" t="inlineStr"/>
-      <c r="G95" s="1" t="inlineStr"/>
-      <c r="H95" s="1" t="inlineStr"/>
-      <c r="I95" s="1" t="inlineStr"/>
-      <c r="J95" s="1" t="inlineStr"/>
-      <c r="K95" s="1" t="inlineStr">
-        <is>
-          <t>L1760: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: barn raising at Mr. Thomas Cowanâ€™s, in the</t>
-        </is>
-      </c>
-      <c r="L95" s="1" t="inlineStr"/>
-      <c r="M95" s="1" t="inlineStr"/>
-      <c r="N95" s="1" t="inlineStr"/>
-      <c r="O95" s="1" t="inlineStr"/>
-      <c r="P95" s="1" t="inlineStr"/>
-      <c r="Q95" s="1" t="inlineStr"/>
-      <c r="R95" s="1" t="inlineStr"/>
-      <c r="S95" s="1" t="inlineStr"/>
-      <c r="T95" s="1" t="inlineStr"/>
-      <c r="U95" s="1" t="inlineStr"/>
-      <c r="V95" s="1" t="inlineStr"/>
-      <c r="W95" s="1" t="inlineStr"/>
-      <c r="X95" s="1" t="inlineStr"/>
-      <c r="Y95" s="1" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="inlineStr"/>
-      <c r="B96" s="1" t="inlineStr"/>
-      <c r="C96" s="1" t="inlineStr"/>
-      <c r="D96" s="1" t="inlineStr"/>
-      <c r="E96" s="1" t="inlineStr"/>
-      <c r="F96" s="1" t="inlineStr"/>
-      <c r="G96" s="1" t="inlineStr"/>
-      <c r="H96" s="1" t="inlineStr"/>
-      <c r="I96" s="1" t="inlineStr"/>
-      <c r="J96" s="1" t="inlineStr"/>
-      <c r="K96" s="1" t="inlineStr">
-        <is>
-          <t>L1826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: formality, pronounced guilty of â€œ fishing,â€�</t>
-        </is>
-      </c>
-      <c r="L96" s="1" t="inlineStr"/>
-      <c r="M96" s="1" t="inlineStr"/>
-      <c r="N96" s="1" t="inlineStr"/>
-      <c r="O96" s="1" t="inlineStr"/>
-      <c r="P96" s="1" t="inlineStr"/>
-      <c r="Q96" s="1" t="inlineStr"/>
-      <c r="R96" s="1" t="inlineStr"/>
-      <c r="S96" s="1" t="inlineStr"/>
-      <c r="T96" s="1" t="inlineStr"/>
-      <c r="U96" s="1" t="inlineStr"/>
-      <c r="V96" s="1" t="inlineStr"/>
-      <c r="W96" s="1" t="inlineStr"/>
-      <c r="X96" s="1" t="inlineStr"/>
-      <c r="Y96" s="1" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="inlineStr"/>
-      <c r="B97" s="1" t="inlineStr"/>
-      <c r="C97" s="1" t="inlineStr"/>
-      <c r="D97" s="1" t="inlineStr"/>
-      <c r="E97" s="1" t="inlineStr"/>
-      <c r="F97" s="1" t="inlineStr"/>
-      <c r="G97" s="1" t="inlineStr"/>
-      <c r="H97" s="1" t="inlineStr"/>
-      <c r="I97" s="1" t="inlineStr"/>
-      <c r="J97" s="1" t="inlineStr"/>
-      <c r="K97" s="1" t="inlineStr">
-        <is>
-          <t>L1865: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”not from inherent richness of texture, for,</t>
-        </is>
-      </c>
-      <c r="L97" s="1" t="inlineStr"/>
-      <c r="M97" s="1" t="inlineStr"/>
-      <c r="N97" s="1" t="inlineStr"/>
-      <c r="O97" s="1" t="inlineStr"/>
-      <c r="P97" s="1" t="inlineStr"/>
-      <c r="Q97" s="1" t="inlineStr"/>
-      <c r="R97" s="1" t="inlineStr"/>
-      <c r="S97" s="1" t="inlineStr"/>
-      <c r="T97" s="1" t="inlineStr"/>
-      <c r="U97" s="1" t="inlineStr"/>
-      <c r="V97" s="1" t="inlineStr"/>
-      <c r="W97" s="1" t="inlineStr"/>
-      <c r="X97" s="1" t="inlineStr"/>
-      <c r="Y97" s="1" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="inlineStr"/>
-      <c r="B98" s="1" t="inlineStr"/>
-      <c r="C98" s="1" t="inlineStr"/>
-      <c r="D98" s="1" t="inlineStr"/>
-      <c r="E98" s="1" t="inlineStr"/>
-      <c r="F98" s="1" t="inlineStr"/>
-      <c r="G98" s="1" t="inlineStr"/>
-      <c r="H98" s="1" t="inlineStr"/>
-      <c r="I98" s="1" t="inlineStr"/>
-      <c r="J98" s="1" t="inlineStr"/>
-      <c r="K98" s="1" t="inlineStr">
-        <is>
-          <t>L1885: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: to make officersâ€™ quarters pretty and home-</t>
-        </is>
-      </c>
-      <c r="L98" s="1" t="inlineStr"/>
-      <c r="M98" s="1" t="inlineStr"/>
-      <c r="N98" s="1" t="inlineStr"/>
-      <c r="O98" s="1" t="inlineStr"/>
-      <c r="P98" s="1" t="inlineStr"/>
-      <c r="Q98" s="1" t="inlineStr"/>
-      <c r="R98" s="1" t="inlineStr"/>
-      <c r="S98" s="1" t="inlineStr"/>
-      <c r="T98" s="1" t="inlineStr"/>
-      <c r="U98" s="1" t="inlineStr"/>
-      <c r="V98" s="1" t="inlineStr"/>
-      <c r="W98" s="1" t="inlineStr"/>
-      <c r="X98" s="1" t="inlineStr"/>
-      <c r="Y98" s="1" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr"/>
-      <c r="B99" s="1" t="inlineStr"/>
-      <c r="C99" s="1" t="inlineStr"/>
-      <c r="D99" s="1" t="inlineStr"/>
-      <c r="E99" s="1" t="inlineStr"/>
-      <c r="F99" s="1" t="inlineStr"/>
-      <c r="G99" s="1" t="inlineStr"/>
-      <c r="H99" s="1" t="inlineStr"/>
-      <c r="I99" s="1" t="inlineStr"/>
-      <c r="J99" s="1" t="inlineStr"/>
-      <c r="K99" s="1" t="inlineStr">
-        <is>
-          <t>L1903: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: even to the handles of thÃ© water-cans and</t>
-        </is>
-      </c>
-      <c r="L99" s="1" t="inlineStr"/>
-      <c r="M99" s="1" t="inlineStr"/>
-      <c r="N99" s="1" t="inlineStr"/>
-      <c r="O99" s="1" t="inlineStr"/>
-      <c r="P99" s="1" t="inlineStr"/>
-      <c r="Q99" s="1" t="inlineStr"/>
-      <c r="R99" s="1" t="inlineStr"/>
-      <c r="S99" s="1" t="inlineStr"/>
-      <c r="T99" s="1" t="inlineStr"/>
-      <c r="U99" s="1" t="inlineStr"/>
-      <c r="V99" s="1" t="inlineStr"/>
-      <c r="W99" s="1" t="inlineStr"/>
-      <c r="X99" s="1" t="inlineStr"/>
-      <c r="Y99" s="1" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr"/>
-      <c r="B100" s="1" t="inlineStr"/>
-      <c r="C100" s="1" t="inlineStr"/>
-      <c r="D100" s="1" t="inlineStr"/>
-      <c r="E100" s="1" t="inlineStr"/>
-      <c r="F100" s="1" t="inlineStr"/>
-      <c r="G100" s="1" t="inlineStr"/>
-      <c r="H100" s="1" t="inlineStr"/>
-      <c r="I100" s="1" t="inlineStr"/>
-      <c r="J100" s="1" t="inlineStr"/>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>L1913: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: varied pages of my past life.â€”Lady Barker's</t>
-        </is>
-      </c>
-      <c r="L100" s="1" t="inlineStr"/>
-      <c r="M100" s="1" t="inlineStr"/>
-      <c r="N100" s="1" t="inlineStr"/>
-      <c r="O100" s="1" t="inlineStr"/>
-      <c r="P100" s="1" t="inlineStr"/>
-      <c r="Q100" s="1" t="inlineStr"/>
-      <c r="R100" s="1" t="inlineStr"/>
-      <c r="S100" s="1" t="inlineStr"/>
-      <c r="T100" s="1" t="inlineStr"/>
-      <c r="U100" s="1" t="inlineStr"/>
-      <c r="V100" s="1" t="inlineStr"/>
-      <c r="W100" s="1" t="inlineStr"/>
-      <c r="X100" s="1" t="inlineStr"/>
-      <c r="Y100" s="1" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr"/>
-      <c r="B101" s="1" t="inlineStr"/>
-      <c r="C101" s="1" t="inlineStr"/>
-      <c r="D101" s="1" t="inlineStr"/>
-      <c r="E101" s="1" t="inlineStr"/>
-      <c r="F101" s="1" t="inlineStr"/>
-      <c r="G101" s="1" t="inlineStr"/>
-      <c r="H101" s="1" t="inlineStr"/>
-      <c r="I101" s="1" t="inlineStr"/>
-      <c r="J101" s="1" t="inlineStr"/>
-      <c r="K101" s="1" t="inlineStr">
-        <is>
-          <t>L1914: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): 4Evening (letter/digit mix) :: " Houses and Housekeepingâ€� in 4Evening</t>
-        </is>
-      </c>
-      <c r="L101" s="1" t="inlineStr"/>
-      <c r="M101" s="1" t="inlineStr"/>
-      <c r="N101" s="1" t="inlineStr"/>
-      <c r="O101" s="1" t="inlineStr"/>
-      <c r="P101" s="1" t="inlineStr"/>
-      <c r="Q101" s="1" t="inlineStr"/>
-      <c r="R101" s="1" t="inlineStr"/>
-      <c r="S101" s="1" t="inlineStr"/>
-      <c r="T101" s="1" t="inlineStr"/>
-      <c r="U101" s="1" t="inlineStr"/>
-      <c r="V101" s="1" t="inlineStr"/>
-      <c r="W101" s="1" t="inlineStr"/>
-      <c r="X101" s="1" t="inlineStr"/>
-      <c r="Y101" s="1" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="inlineStr"/>
-      <c r="B102" s="1" t="inlineStr"/>
-      <c r="C102" s="1" t="inlineStr"/>
-      <c r="D102" s="1" t="inlineStr"/>
-      <c r="E102" s="1" t="inlineStr"/>
-      <c r="F102" s="1" t="inlineStr"/>
-      <c r="G102" s="1" t="inlineStr"/>
-      <c r="H102" s="1" t="inlineStr"/>
-      <c r="I102" s="1" t="inlineStr"/>
-      <c r="J102" s="1" t="inlineStr"/>
-      <c r="K102" s="1" t="inlineStr">
-        <is>
-          <t>L1917: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Superiority OF DUCKSâ€™ Eggs over Hens'</t>
-        </is>
-      </c>
-      <c r="L102" s="1" t="inlineStr"/>
-      <c r="M102" s="1" t="inlineStr"/>
-      <c r="N102" s="1" t="inlineStr"/>
-      <c r="O102" s="1" t="inlineStr"/>
-      <c r="P102" s="1" t="inlineStr"/>
-      <c r="Q102" s="1" t="inlineStr"/>
-      <c r="R102" s="1" t="inlineStr"/>
-      <c r="S102" s="1" t="inlineStr"/>
-      <c r="T102" s="1" t="inlineStr"/>
-      <c r="U102" s="1" t="inlineStr"/>
-      <c r="V102" s="1" t="inlineStr"/>
-      <c r="W102" s="1" t="inlineStr"/>
-      <c r="X102" s="1" t="inlineStr"/>
-      <c r="Y102" s="1" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr"/>
-      <c r="B103" s="1" t="inlineStr"/>
-      <c r="C103" s="1" t="inlineStr"/>
-      <c r="D103" s="1" t="inlineStr"/>
-      <c r="E103" s="1" t="inlineStr"/>
-      <c r="F103" s="1" t="inlineStr"/>
-      <c r="G103" s="1" t="inlineStr"/>
-      <c r="H103" s="1" t="inlineStr"/>
-      <c r="I103" s="1" t="inlineStr"/>
-      <c r="J103" s="1" t="inlineStr"/>
-      <c r="K103" s="1" t="inlineStr">
-        <is>
-          <t>L1918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Eggs.â€”The following details are given as the</t>
-        </is>
-      </c>
-      <c r="L103" s="1" t="inlineStr"/>
-      <c r="M103" s="1" t="inlineStr"/>
-      <c r="N103" s="1" t="inlineStr"/>
-      <c r="O103" s="1" t="inlineStr"/>
-      <c r="P103" s="1" t="inlineStr"/>
-      <c r="Q103" s="1" t="inlineStr"/>
-      <c r="R103" s="1" t="inlineStr"/>
-      <c r="S103" s="1" t="inlineStr"/>
-      <c r="T103" s="1" t="inlineStr"/>
-      <c r="U103" s="1" t="inlineStr"/>
-      <c r="V103" s="1" t="inlineStr"/>
-      <c r="W103" s="1" t="inlineStr"/>
-      <c r="X103" s="1" t="inlineStr"/>
-      <c r="Y103" s="1" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr"/>
-      <c r="B104" s="1" t="inlineStr"/>
-      <c r="C104" s="1" t="inlineStr"/>
-      <c r="D104" s="1" t="inlineStr"/>
-      <c r="E104" s="1" t="inlineStr"/>
-      <c r="F104" s="1" t="inlineStr"/>
-      <c r="G104" s="1" t="inlineStr"/>
-      <c r="H104" s="1" t="inlineStr"/>
-      <c r="I104" s="1" t="inlineStr"/>
-      <c r="J104" s="1" t="inlineStr"/>
-      <c r="K104" s="1" t="inlineStr">
-        <is>
-          <t>L1923: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: This is a free country, and men may say and 5 not lose histime,"for being a â€œ man of</t>
-        </is>
-      </c>
-      <c r="L104" s="1" t="inlineStr"/>
-      <c r="M104" s="1" t="inlineStr"/>
-      <c r="N104" s="1" t="inlineStr"/>
-      <c r="O104" s="1" t="inlineStr"/>
-      <c r="P104" s="1" t="inlineStr"/>
-      <c r="Q104" s="1" t="inlineStr"/>
-      <c r="R104" s="1" t="inlineStr"/>
-      <c r="S104" s="1" t="inlineStr"/>
-      <c r="T104" s="1" t="inlineStr"/>
-      <c r="U104" s="1" t="inlineStr"/>
-      <c r="V104" s="1" t="inlineStr"/>
-      <c r="W104" s="1" t="inlineStr"/>
-      <c r="X104" s="1" t="inlineStr"/>
-      <c r="Y104" s="1" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr"/>
-      <c r="B105" s="1" t="inlineStr"/>
-      <c r="C105" s="1" t="inlineStr"/>
-      <c r="D105" s="1" t="inlineStr"/>
-      <c r="E105" s="1" t="inlineStr"/>
-      <c r="F105" s="1" t="inlineStr"/>
-      <c r="G105" s="1" t="inlineStr"/>
-      <c r="H105" s="1" t="inlineStr"/>
-      <c r="I105" s="1" t="inlineStr"/>
-      <c r="J105" s="1" t="inlineStr"/>
-      <c r="K105" s="1" t="inlineStr">
-        <is>
-          <t>L1928: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: INFORMAL PEOPLE. â€” Preserve us from</t>
-        </is>
-      </c>
-      <c r="L105" s="1" t="inlineStr"/>
-      <c r="M105" s="1" t="inlineStr"/>
-      <c r="N105" s="1" t="inlineStr"/>
-      <c r="O105" s="1" t="inlineStr"/>
-      <c r="P105" s="1" t="inlineStr"/>
-      <c r="Q105" s="1" t="inlineStr"/>
-      <c r="R105" s="1" t="inlineStr"/>
-      <c r="S105" s="1" t="inlineStr"/>
-      <c r="T105" s="1" t="inlineStr"/>
-      <c r="U105" s="1" t="inlineStr"/>
-      <c r="V105" s="1" t="inlineStr"/>
-      <c r="W105" s="1" t="inlineStr"/>
-      <c r="X105" s="1" t="inlineStr"/>
-      <c r="Y105" s="1" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="inlineStr"/>
-      <c r="B106" s="1" t="inlineStr"/>
-      <c r="C106" s="1" t="inlineStr"/>
-      <c r="D106" s="1" t="inlineStr"/>
-      <c r="E106" s="1" t="inlineStr"/>
-      <c r="F106" s="1" t="inlineStr"/>
-      <c r="G106" s="1" t="inlineStr"/>
-      <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr"/>
-      <c r="J106" s="1" t="inlineStr"/>
-      <c r="K106" s="1" t="inlineStr">
-        <is>
-          <t>L1929: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: uncermonious peopleâ€”those men and wo-</t>
-        </is>
-      </c>
-      <c r="L106" s="1" t="inlineStr"/>
-      <c r="M106" s="1" t="inlineStr"/>
-      <c r="N106" s="1" t="inlineStr"/>
-      <c r="O106" s="1" t="inlineStr"/>
-      <c r="P106" s="1" t="inlineStr"/>
-      <c r="Q106" s="1" t="inlineStr"/>
-      <c r="R106" s="1" t="inlineStr"/>
-      <c r="S106" s="1" t="inlineStr"/>
-      <c r="T106" s="1" t="inlineStr"/>
-      <c r="U106" s="1" t="inlineStr"/>
-      <c r="V106" s="1" t="inlineStr"/>
-      <c r="W106" s="1" t="inlineStr"/>
-      <c r="X106" s="1" t="inlineStr"/>
-      <c r="Y106" s="1" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="inlineStr"/>
-      <c r="B107" s="1" t="inlineStr"/>
-      <c r="C107" s="1" t="inlineStr"/>
-      <c r="D107" s="1" t="inlineStr"/>
-      <c r="E107" s="1" t="inlineStr"/>
-      <c r="F107" s="1" t="inlineStr"/>
-      <c r="G107" s="1" t="inlineStr"/>
-      <c r="H107" s="1" t="inlineStr"/>
-      <c r="I107" s="1" t="inlineStr"/>
-      <c r="J107" s="1" t="inlineStr"/>
-      <c r="K107" s="1" t="inlineStr">
-        <is>
-          <t>L1931: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”who are always perfectly at home in</t>
-        </is>
-      </c>
-      <c r="L107" s="1" t="inlineStr"/>
-      <c r="M107" s="1" t="inlineStr"/>
-      <c r="N107" s="1" t="inlineStr"/>
-      <c r="O107" s="1" t="inlineStr"/>
-      <c r="P107" s="1" t="inlineStr"/>
-      <c r="Q107" s="1" t="inlineStr"/>
-      <c r="R107" s="1" t="inlineStr"/>
-      <c r="S107" s="1" t="inlineStr"/>
-      <c r="T107" s="1" t="inlineStr"/>
-      <c r="U107" s="1" t="inlineStr"/>
-      <c r="V107" s="1" t="inlineStr"/>
-      <c r="W107" s="1" t="inlineStr"/>
-      <c r="X107" s="1" t="inlineStr"/>
-      <c r="Y107" s="1" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="inlineStr"/>
-      <c r="B108" s="1" t="inlineStr"/>
-      <c r="C108" s="1" t="inlineStr"/>
-      <c r="D108" s="1" t="inlineStr"/>
-      <c r="E108" s="1" t="inlineStr"/>
-      <c r="F108" s="1" t="inlineStr"/>
-      <c r="G108" s="1" t="inlineStr"/>
-      <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr"/>
-      <c r="J108" s="1" t="inlineStr"/>
-      <c r="K108" s="1" t="inlineStr">
-        <is>
-          <t>L1943: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: in,â€� and they will come right up to your</t>
-        </is>
-      </c>
-      <c r="L108" s="1" t="inlineStr"/>
-      <c r="M108" s="1" t="inlineStr"/>
-      <c r="N108" s="1" t="inlineStr"/>
-      <c r="O108" s="1" t="inlineStr"/>
-      <c r="P108" s="1" t="inlineStr"/>
-      <c r="Q108" s="1" t="inlineStr"/>
-      <c r="R108" s="1" t="inlineStr"/>
-      <c r="S108" s="1" t="inlineStr"/>
-      <c r="T108" s="1" t="inlineStr"/>
-      <c r="U108" s="1" t="inlineStr"/>
-      <c r="V108" s="1" t="inlineStr"/>
-      <c r="W108" s="1" t="inlineStr"/>
-      <c r="X108" s="1" t="inlineStr"/>
-      <c r="Y108" s="1" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr"/>
-      <c r="B109" s="1" t="inlineStr"/>
-      <c r="C109" s="1" t="inlineStr"/>
-      <c r="D109" s="1" t="inlineStr"/>
-      <c r="E109" s="1" t="inlineStr"/>
-      <c r="F109" s="1" t="inlineStr"/>
-      <c r="G109" s="1" t="inlineStr"/>
-      <c r="H109" s="1" t="inlineStr"/>
-      <c r="I109" s="1" t="inlineStr"/>
-      <c r="J109" s="1" t="inlineStr"/>
-      <c r="K109" s="1" t="inlineStr">
-        <is>
-          <t>L1973: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œcrystalized,â€� to use Mr. Blake's expression,</t>
-        </is>
-      </c>
-      <c r="L109" s="1" t="inlineStr"/>
-      <c r="M109" s="1" t="inlineStr"/>
-      <c r="N109" s="1" t="inlineStr"/>
-      <c r="O109" s="1" t="inlineStr"/>
-      <c r="P109" s="1" t="inlineStr"/>
-      <c r="Q109" s="1" t="inlineStr"/>
-      <c r="R109" s="1" t="inlineStr"/>
-      <c r="S109" s="1" t="inlineStr"/>
-      <c r="T109" s="1" t="inlineStr"/>
-      <c r="U109" s="1" t="inlineStr"/>
-      <c r="V109" s="1" t="inlineStr"/>
-      <c r="W109" s="1" t="inlineStr"/>
-      <c r="X109" s="1" t="inlineStr"/>
-      <c r="Y109" s="1" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="inlineStr"/>
-      <c r="B110" s="1" t="inlineStr"/>
-      <c r="C110" s="1" t="inlineStr"/>
-      <c r="D110" s="1" t="inlineStr"/>
-      <c r="E110" s="1" t="inlineStr"/>
-      <c r="F110" s="1" t="inlineStr"/>
-      <c r="G110" s="1" t="inlineStr"/>
-      <c r="H110" s="1" t="inlineStr"/>
-      <c r="I110" s="1" t="inlineStr"/>
-      <c r="J110" s="1" t="inlineStr"/>
-      <c r="K110" s="1" t="inlineStr">
-        <is>
-          <t>L1976: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the famous Aurora speechâ€”a fair field and</t>
-        </is>
-      </c>
-      <c r="L110" s="1" t="inlineStr"/>
-      <c r="M110" s="1" t="inlineStr"/>
-      <c r="N110" s="1" t="inlineStr"/>
-      <c r="O110" s="1" t="inlineStr"/>
-      <c r="P110" s="1" t="inlineStr"/>
-      <c r="Q110" s="1" t="inlineStr"/>
-      <c r="R110" s="1" t="inlineStr"/>
-      <c r="S110" s="1" t="inlineStr"/>
-      <c r="T110" s="1" t="inlineStr"/>
-      <c r="U110" s="1" t="inlineStr"/>
-      <c r="V110" s="1" t="inlineStr"/>
-      <c r="W110" s="1" t="inlineStr"/>
-      <c r="X110" s="1" t="inlineStr"/>
-      <c r="Y110" s="1" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="inlineStr"/>
-      <c r="B111" s="1" t="inlineStr"/>
-      <c r="C111" s="1" t="inlineStr"/>
-      <c r="D111" s="1" t="inlineStr"/>
-      <c r="E111" s="1" t="inlineStr"/>
-      <c r="F111" s="1" t="inlineStr"/>
-      <c r="G111" s="1" t="inlineStr"/>
-      <c r="H111" s="1" t="inlineStr"/>
-      <c r="I111" s="1" t="inlineStr"/>
-      <c r="J111" s="1" t="inlineStr"/>
-      <c r="K111" s="1" t="inlineStr">
-        <is>
-          <t>L2007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œ freely as he wished." This is but a sample</t>
-        </is>
-      </c>
-      <c r="L111" s="1" t="inlineStr"/>
-      <c r="M111" s="1" t="inlineStr"/>
-      <c r="N111" s="1" t="inlineStr"/>
-      <c r="O111" s="1" t="inlineStr"/>
-      <c r="P111" s="1" t="inlineStr"/>
-      <c r="Q111" s="1" t="inlineStr"/>
-      <c r="R111" s="1" t="inlineStr"/>
-      <c r="S111" s="1" t="inlineStr"/>
-      <c r="T111" s="1" t="inlineStr"/>
-      <c r="U111" s="1" t="inlineStr"/>
-      <c r="V111" s="1" t="inlineStr"/>
-      <c r="W111" s="1" t="inlineStr"/>
-      <c r="X111" s="1" t="inlineStr"/>
-      <c r="Y111" s="1" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="inlineStr"/>
-      <c r="B112" s="1" t="inlineStr"/>
-      <c r="C112" s="1" t="inlineStr"/>
-      <c r="D112" s="1" t="inlineStr"/>
-      <c r="E112" s="1" t="inlineStr"/>
-      <c r="F112" s="1" t="inlineStr"/>
-      <c r="G112" s="1" t="inlineStr"/>
-      <c r="H112" s="1" t="inlineStr"/>
-      <c r="I112" s="1" t="inlineStr"/>
-      <c r="J112" s="1" t="inlineStr"/>
-      <c r="K112" s="1" t="inlineStr">
-        <is>
-          <t>L2043: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: â€”" You know Iâ€™m too much at home in your</t>
-        </is>
-      </c>
-      <c r="L112" s="1" t="inlineStr"/>
-      <c r="M112" s="1" t="inlineStr"/>
-      <c r="N112" s="1" t="inlineStr"/>
-      <c r="O112" s="1" t="inlineStr"/>
-      <c r="P112" s="1" t="inlineStr"/>
-      <c r="Q112" s="1" t="inlineStr"/>
-      <c r="R112" s="1" t="inlineStr"/>
-      <c r="S112" s="1" t="inlineStr"/>
-      <c r="T112" s="1" t="inlineStr"/>
-      <c r="U112" s="1" t="inlineStr"/>
-      <c r="V112" s="1" t="inlineStr"/>
-      <c r="W112" s="1" t="inlineStr"/>
-      <c r="X112" s="1" t="inlineStr"/>
-      <c r="Y112" s="1" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr"/>
-      <c r="B113" s="1" t="inlineStr"/>
-      <c r="C113" s="1" t="inlineStr"/>
-      <c r="D113" s="1" t="inlineStr"/>
-      <c r="E113" s="1" t="inlineStr"/>
-      <c r="F113" s="1" t="inlineStr"/>
-      <c r="G113" s="1" t="inlineStr"/>
-      <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr"/>
-      <c r="J113" s="1" t="inlineStr"/>
-      <c r="K113" s="1" t="inlineStr">
-        <is>
-          <t>L2044: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: house to go hungry, my dear "â€”and any</t>
-        </is>
-      </c>
-      <c r="L113" s="1" t="inlineStr"/>
-      <c r="M113" s="1" t="inlineStr"/>
-      <c r="N113" s="1" t="inlineStr"/>
-      <c r="O113" s="1" t="inlineStr"/>
-      <c r="P113" s="1" t="inlineStr"/>
-      <c r="Q113" s="1" t="inlineStr"/>
-      <c r="R113" s="1" t="inlineStr"/>
-      <c r="S113" s="1" t="inlineStr"/>
-      <c r="T113" s="1" t="inlineStr"/>
-      <c r="U113" s="1" t="inlineStr"/>
-      <c r="V113" s="1" t="inlineStr"/>
-      <c r="W113" s="1" t="inlineStr"/>
-      <c r="X113" s="1" t="inlineStr"/>
-      <c r="Y113" s="1" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="inlineStr"/>
-      <c r="B114" s="1" t="inlineStr"/>
-      <c r="C114" s="1" t="inlineStr"/>
-      <c r="D114" s="1" t="inlineStr"/>
-      <c r="E114" s="1" t="inlineStr"/>
-      <c r="F114" s="1" t="inlineStr"/>
-      <c r="G114" s="1" t="inlineStr"/>
-      <c r="H114" s="1" t="inlineStr"/>
-      <c r="I114" s="1" t="inlineStr"/>
-      <c r="J114" s="1" t="inlineStr"/>
-      <c r="K114" s="1" t="inlineStr">
-        <is>
-          <t>L2053: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: but make myself at home everywhere, soâ€™</t>
-        </is>
-      </c>
-      <c r="L114" s="1" t="inlineStr"/>
-      <c r="M114" s="1" t="inlineStr"/>
-      <c r="N114" s="1" t="inlineStr"/>
-      <c r="O114" s="1" t="inlineStr"/>
-      <c r="P114" s="1" t="inlineStr"/>
-      <c r="Q114" s="1" t="inlineStr"/>
-      <c r="R114" s="1" t="inlineStr"/>
-      <c r="S114" s="1" t="inlineStr"/>
-      <c r="T114" s="1" t="inlineStr"/>
-      <c r="U114" s="1" t="inlineStr"/>
-      <c r="V114" s="1" t="inlineStr"/>
-      <c r="W114" s="1" t="inlineStr"/>
-      <c r="X114" s="1" t="inlineStr"/>
-      <c r="Y114" s="1" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="inlineStr"/>
-      <c r="B115" s="1" t="inlineStr"/>
-      <c r="C115" s="1" t="inlineStr"/>
-      <c r="D115" s="1" t="inlineStr"/>
-      <c r="E115" s="1" t="inlineStr"/>
-      <c r="F115" s="1" t="inlineStr"/>
-      <c r="G115" s="1" t="inlineStr"/>
-      <c r="H115" s="1" t="inlineStr"/>
-      <c r="I115" s="1" t="inlineStr"/>
-      <c r="J115" s="1" t="inlineStr"/>
-      <c r="K115" s="1" t="inlineStr">
-        <is>
-          <t>L2054: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: donâ€™t put yourself out to entertain me !"</t>
-        </is>
-      </c>
-      <c r="L115" s="1" t="inlineStr"/>
-      <c r="M115" s="1" t="inlineStr"/>
-      <c r="N115" s="1" t="inlineStr"/>
-      <c r="O115" s="1" t="inlineStr"/>
-      <c r="P115" s="1" t="inlineStr"/>
-      <c r="Q115" s="1" t="inlineStr"/>
-      <c r="R115" s="1" t="inlineStr"/>
-      <c r="S115" s="1" t="inlineStr"/>
-      <c r="T115" s="1" t="inlineStr"/>
-      <c r="U115" s="1" t="inlineStr"/>
-      <c r="V115" s="1" t="inlineStr"/>
-      <c r="W115" s="1" t="inlineStr"/>
-      <c r="X115" s="1" t="inlineStr"/>
-      <c r="Y115" s="1" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="inlineStr"/>
-      <c r="B116" s="1" t="inlineStr"/>
-      <c r="C116" s="1" t="inlineStr"/>
-      <c r="D116" s="1" t="inlineStr"/>
-      <c r="E116" s="1" t="inlineStr"/>
-      <c r="F116" s="1" t="inlineStr"/>
-      <c r="G116" s="1" t="inlineStr"/>
-      <c r="H116" s="1" t="inlineStr"/>
-      <c r="I116" s="1" t="inlineStr"/>
-      <c r="J116" s="1" t="inlineStr"/>
-      <c r="K116" s="1" t="inlineStr">
-        <is>
-          <t>L2089: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of whom bet the other that he couldnâ€™t carry</t>
-        </is>
-      </c>
-      <c r="L116" s="1" t="inlineStr"/>
-      <c r="M116" s="1" t="inlineStr"/>
-      <c r="N116" s="1" t="inlineStr"/>
-      <c r="O116" s="1" t="inlineStr"/>
-      <c r="P116" s="1" t="inlineStr"/>
-      <c r="Q116" s="1" t="inlineStr"/>
-      <c r="R116" s="1" t="inlineStr"/>
-      <c r="S116" s="1" t="inlineStr"/>
-      <c r="T116" s="1" t="inlineStr"/>
-      <c r="U116" s="1" t="inlineStr"/>
-      <c r="V116" s="1" t="inlineStr"/>
-      <c r="W116" s="1" t="inlineStr"/>
-      <c r="X116" s="1" t="inlineStr"/>
-      <c r="Y116" s="1" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="inlineStr"/>
-      <c r="B117" s="1" t="inlineStr"/>
-      <c r="C117" s="1" t="inlineStr"/>
-      <c r="D117" s="1" t="inlineStr"/>
-      <c r="E117" s="1" t="inlineStr"/>
-      <c r="F117" s="1" t="inlineStr"/>
-      <c r="G117" s="1" t="inlineStr"/>
-      <c r="H117" s="1" t="inlineStr"/>
-      <c r="I117" s="1" t="inlineStr"/>
-      <c r="J117" s="1" t="inlineStr"/>
-      <c r="K117" s="1" t="inlineStr">
-        <is>
-          <t>L2155: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: one reason is that the poor manâ€™s cow gets a</t>
-        </is>
-      </c>
-      <c r="L117" s="1" t="inlineStr"/>
-      <c r="M117" s="1" t="inlineStr"/>
-      <c r="N117" s="1" t="inlineStr"/>
-      <c r="O117" s="1" t="inlineStr"/>
-      <c r="P117" s="1" t="inlineStr"/>
-      <c r="Q117" s="1" t="inlineStr"/>
-      <c r="R117" s="1" t="inlineStr"/>
-      <c r="S117" s="1" t="inlineStr"/>
-      <c r="T117" s="1" t="inlineStr"/>
-      <c r="U117" s="1" t="inlineStr"/>
-      <c r="V117" s="1" t="inlineStr"/>
-      <c r="W117" s="1" t="inlineStr"/>
-      <c r="X117" s="1" t="inlineStr"/>
-      <c r="Y117" s="1" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="inlineStr"/>
-      <c r="B118" s="1" t="inlineStr"/>
-      <c r="C118" s="1" t="inlineStr"/>
-      <c r="D118" s="1" t="inlineStr"/>
-      <c r="E118" s="1" t="inlineStr"/>
-      <c r="F118" s="1" t="inlineStr"/>
-      <c r="G118" s="1" t="inlineStr"/>
-      <c r="H118" s="1" t="inlineStr"/>
-      <c r="I118" s="1" t="inlineStr"/>
-      <c r="J118" s="1" t="inlineStr"/>
-      <c r="K118" s="1" t="inlineStr">
-        <is>
-          <t>L2166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Vicompte de Hâ€”was seventy years old,</t>
-        </is>
-      </c>
-      <c r="L118" s="1" t="inlineStr"/>
-      <c r="M118" s="1" t="inlineStr"/>
-      <c r="N118" s="1" t="inlineStr"/>
-      <c r="O118" s="1" t="inlineStr"/>
-      <c r="P118" s="1" t="inlineStr"/>
-      <c r="Q118" s="1" t="inlineStr"/>
-      <c r="R118" s="1" t="inlineStr"/>
-      <c r="S118" s="1" t="inlineStr"/>
-      <c r="T118" s="1" t="inlineStr"/>
-      <c r="U118" s="1" t="inlineStr"/>
-      <c r="V118" s="1" t="inlineStr"/>
-      <c r="W118" s="1" t="inlineStr"/>
-      <c r="X118" s="1" t="inlineStr"/>
-      <c r="Y118" s="1" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="inlineStr"/>
-      <c r="B119" s="1" t="inlineStr"/>
-      <c r="C119" s="1" t="inlineStr"/>
-      <c r="D119" s="1" t="inlineStr"/>
-      <c r="E119" s="1" t="inlineStr"/>
-      <c r="F119" s="1" t="inlineStr"/>
-      <c r="G119" s="1" t="inlineStr"/>
-      <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr"/>
-      <c r="J119" s="1" t="inlineStr"/>
-      <c r="K119" s="1" t="inlineStr">
-        <is>
-          <t>L2205: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: is chiefly by Dr. Haneyâ€™s election last</t>
-        </is>
-      </c>
-      <c r="L119" s="1" t="inlineStr"/>
-      <c r="M119" s="1" t="inlineStr"/>
-      <c r="N119" s="1" t="inlineStr"/>
-      <c r="O119" s="1" t="inlineStr"/>
-      <c r="P119" s="1" t="inlineStr"/>
-      <c r="Q119" s="1" t="inlineStr"/>
-      <c r="R119" s="1" t="inlineStr"/>
-      <c r="S119" s="1" t="inlineStr"/>
-      <c r="T119" s="1" t="inlineStr"/>
-      <c r="U119" s="1" t="inlineStr"/>
-      <c r="V119" s="1" t="inlineStr"/>
-      <c r="W119" s="1" t="inlineStr"/>
-      <c r="X119" s="1" t="inlineStr"/>
-      <c r="Y119" s="1" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="inlineStr"/>
-      <c r="B120" s="1" t="inlineStr"/>
-      <c r="C120" s="1" t="inlineStr"/>
-      <c r="D120" s="1" t="inlineStr"/>
-      <c r="E120" s="1" t="inlineStr"/>
-      <c r="F120" s="1" t="inlineStr"/>
-      <c r="G120" s="1" t="inlineStr"/>
-      <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr"/>
-      <c r="J120" s="1" t="inlineStr"/>
-      <c r="K120" s="1" t="inlineStr">
-        <is>
-          <t>L2218: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Haneyâ€™s opponent, is unknown, and, from</t>
-        </is>
-      </c>
-      <c r="L120" s="1" t="inlineStr"/>
-      <c r="M120" s="1" t="inlineStr"/>
-      <c r="N120" s="1" t="inlineStr"/>
-      <c r="O120" s="1" t="inlineStr"/>
-      <c r="P120" s="1" t="inlineStr"/>
-      <c r="Q120" s="1" t="inlineStr"/>
-      <c r="R120" s="1" t="inlineStr"/>
-      <c r="S120" s="1" t="inlineStr"/>
-      <c r="T120" s="1" t="inlineStr"/>
-      <c r="U120" s="1" t="inlineStr"/>
-      <c r="V120" s="1" t="inlineStr"/>
-      <c r="W120" s="1" t="inlineStr"/>
-      <c r="X120" s="1" t="inlineStr"/>
-      <c r="Y120" s="1" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="inlineStr"/>
-      <c r="B121" s="1" t="inlineStr"/>
-      <c r="C121" s="1" t="inlineStr"/>
-      <c r="D121" s="1" t="inlineStr"/>
-      <c r="E121" s="1" t="inlineStr"/>
-      <c r="F121" s="1" t="inlineStr"/>
-      <c r="G121" s="1" t="inlineStr"/>
-      <c r="H121" s="1" t="inlineStr"/>
-      <c r="I121" s="1" t="inlineStr"/>
-      <c r="J121" s="1" t="inlineStr"/>
-      <c r="K121" s="1" t="inlineStr">
-        <is>
-          <t>L2242: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Welland Tribune.</t>
-        </is>
-      </c>
-      <c r="L121" s="1" t="inlineStr"/>
-      <c r="M121" s="1" t="inlineStr"/>
-      <c r="N121" s="1" t="inlineStr"/>
-      <c r="O121" s="1" t="inlineStr"/>
-      <c r="P121" s="1" t="inlineStr"/>
-      <c r="Q121" s="1" t="inlineStr"/>
-      <c r="R121" s="1" t="inlineStr"/>
-      <c r="S121" s="1" t="inlineStr"/>
-      <c r="T121" s="1" t="inlineStr"/>
-      <c r="U121" s="1" t="inlineStr"/>
-      <c r="V121" s="1" t="inlineStr"/>
-      <c r="W121" s="1" t="inlineStr"/>
-      <c r="X121" s="1" t="inlineStr"/>
-      <c r="Y121" s="1" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="inlineStr"/>
-      <c r="B122" s="1" t="inlineStr"/>
-      <c r="C122" s="1" t="inlineStr"/>
-      <c r="D122" s="1" t="inlineStr"/>
-      <c r="E122" s="1" t="inlineStr"/>
-      <c r="F122" s="1" t="inlineStr"/>
-      <c r="G122" s="1" t="inlineStr"/>
-      <c r="H122" s="1" t="inlineStr"/>
-      <c r="I122" s="1" t="inlineStr"/>
-      <c r="J122" s="1" t="inlineStr"/>
-      <c r="K122" s="1" t="inlineStr">
-        <is>
-          <t>L2253: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tion in Roman Catholic circles.â€”New York</t>
-        </is>
-      </c>
-      <c r="L122" s="1" t="inlineStr"/>
-      <c r="M122" s="1" t="inlineStr"/>
-      <c r="N122" s="1" t="inlineStr"/>
-      <c r="O122" s="1" t="inlineStr"/>
-      <c r="P122" s="1" t="inlineStr"/>
-      <c r="Q122" s="1" t="inlineStr"/>
-      <c r="R122" s="1" t="inlineStr"/>
-      <c r="S122" s="1" t="inlineStr"/>
-      <c r="T122" s="1" t="inlineStr"/>
-      <c r="U122" s="1" t="inlineStr"/>
-      <c r="V122" s="1" t="inlineStr"/>
-      <c r="W122" s="1" t="inlineStr"/>
-      <c r="X122" s="1" t="inlineStr"/>
-      <c r="Y122" s="1" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="inlineStr"/>
-      <c r="B123" s="1" t="inlineStr"/>
-      <c r="C123" s="1" t="inlineStr"/>
-      <c r="D123" s="1" t="inlineStr"/>
-      <c r="E123" s="1" t="inlineStr"/>
-      <c r="F123" s="1" t="inlineStr"/>
-      <c r="G123" s="1" t="inlineStr"/>
-      <c r="H123" s="1" t="inlineStr"/>
-      <c r="I123" s="1" t="inlineStr"/>
-      <c r="J123" s="1" t="inlineStr"/>
-      <c r="K123" s="1" t="inlineStr">
-        <is>
-          <t>L2256: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: HONORING THE DEAD.â€”The graves in old</t>
-        </is>
-      </c>
-      <c r="L123" s="1" t="inlineStr"/>
-      <c r="M123" s="1" t="inlineStr"/>
-      <c r="N123" s="1" t="inlineStr"/>
-      <c r="O123" s="1" t="inlineStr"/>
-      <c r="P123" s="1" t="inlineStr"/>
-      <c r="Q123" s="1" t="inlineStr"/>
-      <c r="R123" s="1" t="inlineStr"/>
-      <c r="S123" s="1" t="inlineStr"/>
-      <c r="T123" s="1" t="inlineStr"/>
-      <c r="U123" s="1" t="inlineStr"/>
-      <c r="V123" s="1" t="inlineStr"/>
-      <c r="W123" s="1" t="inlineStr"/>
-      <c r="X123" s="1" t="inlineStr"/>
-      <c r="Y123" s="1" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="inlineStr"/>
-      <c r="B124" s="1" t="inlineStr"/>
-      <c r="C124" s="1" t="inlineStr"/>
-      <c r="D124" s="1" t="inlineStr"/>
-      <c r="E124" s="1" t="inlineStr"/>
-      <c r="F124" s="1" t="inlineStr"/>
-      <c r="G124" s="1" t="inlineStr"/>
-      <c r="H124" s="1" t="inlineStr"/>
-      <c r="I124" s="1" t="inlineStr"/>
-      <c r="J124" s="1" t="inlineStr"/>
-      <c r="K124" s="1" t="inlineStr">
-        <is>
-          <t>L2280: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: begun in Blackwoodâ€™s Magazine, i^ said to be</t>
-        </is>
-      </c>
-      <c r="L124" s="1" t="inlineStr"/>
-      <c r="M124" s="1" t="inlineStr"/>
-      <c r="N124" s="1" t="inlineStr"/>
-      <c r="O124" s="1" t="inlineStr"/>
-      <c r="P124" s="1" t="inlineStr"/>
-      <c r="Q124" s="1" t="inlineStr"/>
-      <c r="R124" s="1" t="inlineStr"/>
-      <c r="S124" s="1" t="inlineStr"/>
-      <c r="T124" s="1" t="inlineStr"/>
-      <c r="U124" s="1" t="inlineStr"/>
-      <c r="V124" s="1" t="inlineStr"/>
-      <c r="W124" s="1" t="inlineStr"/>
-      <c r="X124" s="1" t="inlineStr"/>
-      <c r="Y124" s="1" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="inlineStr"/>
-      <c r="B125" s="1" t="inlineStr"/>
-      <c r="C125" s="1" t="inlineStr"/>
-      <c r="D125" s="1" t="inlineStr"/>
-      <c r="E125" s="1" t="inlineStr"/>
-      <c r="F125" s="1" t="inlineStr"/>
-      <c r="G125" s="1" t="inlineStr"/>
-      <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr"/>
-      <c r="J125" s="1" t="inlineStr"/>
-      <c r="K125" s="1" t="inlineStr">
-        <is>
-          <t>L2294: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ardent lover of Meyerbeerâ€™s music, he</t>
-        </is>
-      </c>
-      <c r="L125" s="1" t="inlineStr"/>
-      <c r="M125" s="1" t="inlineStr"/>
-      <c r="N125" s="1" t="inlineStr"/>
-      <c r="O125" s="1" t="inlineStr"/>
-      <c r="P125" s="1" t="inlineStr"/>
-      <c r="Q125" s="1" t="inlineStr"/>
-      <c r="R125" s="1" t="inlineStr"/>
-      <c r="S125" s="1" t="inlineStr"/>
-      <c r="T125" s="1" t="inlineStr"/>
-      <c r="U125" s="1" t="inlineStr"/>
-      <c r="V125" s="1" t="inlineStr"/>
-      <c r="W125" s="1" t="inlineStr"/>
-      <c r="X125" s="1" t="inlineStr"/>
-      <c r="Y125" s="1" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="inlineStr"/>
-      <c r="B126" s="1" t="inlineStr"/>
-      <c r="C126" s="1" t="inlineStr"/>
-      <c r="D126" s="1" t="inlineStr"/>
-      <c r="E126" s="1" t="inlineStr"/>
-      <c r="F126" s="1" t="inlineStr"/>
-      <c r="G126" s="1" t="inlineStr"/>
-      <c r="H126" s="1" t="inlineStr"/>
-      <c r="I126" s="1" t="inlineStr"/>
-      <c r="J126" s="1" t="inlineStr"/>
-      <c r="K126" s="1" t="inlineStr">
-        <is>
-          <t>L2334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Avowal, a four-year-old coltâ€”one-third of</t>
-        </is>
-      </c>
-      <c r="L126" s="1" t="inlineStr"/>
-      <c r="M126" s="1" t="inlineStr"/>
-      <c r="N126" s="1" t="inlineStr"/>
-      <c r="O126" s="1" t="inlineStr"/>
-      <c r="P126" s="1" t="inlineStr"/>
-      <c r="Q126" s="1" t="inlineStr"/>
-      <c r="R126" s="1" t="inlineStr"/>
-      <c r="S126" s="1" t="inlineStr"/>
-      <c r="T126" s="1" t="inlineStr"/>
-      <c r="U126" s="1" t="inlineStr"/>
-      <c r="V126" s="1" t="inlineStr"/>
-      <c r="W126" s="1" t="inlineStr"/>
-      <c r="X126" s="1" t="inlineStr"/>
-      <c r="Y126" s="1" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="inlineStr"/>
-      <c r="B127" s="1" t="inlineStr"/>
-      <c r="C127" s="1" t="inlineStr"/>
-      <c r="D127" s="1" t="inlineStr"/>
-      <c r="E127" s="1" t="inlineStr"/>
-      <c r="F127" s="1" t="inlineStr"/>
-      <c r="G127" s="1" t="inlineStr"/>
-      <c r="H127" s="1" t="inlineStr"/>
-      <c r="I127" s="1" t="inlineStr"/>
-      <c r="J127" s="1" t="inlineStr"/>
-      <c r="K127" s="1" t="inlineStr">
-        <is>
-          <t>L2336: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Arab and two-thirds of English bloodâ€”and</t>
-        </is>
-      </c>
-      <c r="L127" s="1" t="inlineStr"/>
-      <c r="M127" s="1" t="inlineStr"/>
-      <c r="N127" s="1" t="inlineStr"/>
-      <c r="O127" s="1" t="inlineStr"/>
-      <c r="P127" s="1" t="inlineStr"/>
-      <c r="Q127" s="1" t="inlineStr"/>
-      <c r="R127" s="1" t="inlineStr"/>
-      <c r="S127" s="1" t="inlineStr"/>
-      <c r="T127" s="1" t="inlineStr"/>
-      <c r="U127" s="1" t="inlineStr"/>
-      <c r="V127" s="1" t="inlineStr"/>
-      <c r="W127" s="1" t="inlineStr"/>
-      <c r="X127" s="1" t="inlineStr"/>
-      <c r="Y127" s="1" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="inlineStr"/>
-      <c r="B128" s="1" t="inlineStr"/>
-      <c r="C128" s="1" t="inlineStr"/>
-      <c r="D128" s="1" t="inlineStr"/>
-      <c r="E128" s="1" t="inlineStr"/>
-      <c r="F128" s="1" t="inlineStr"/>
-      <c r="G128" s="1" t="inlineStr"/>
-      <c r="H128" s="1" t="inlineStr"/>
-      <c r="I128" s="1" t="inlineStr"/>
-      <c r="J128" s="1" t="inlineStr"/>
-      <c r="K128" s="1" t="inlineStr">
-        <is>
-          <t>L2367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: only.â€”Practical Magazine.</t>
-        </is>
-      </c>
-      <c r="L128" s="1" t="inlineStr"/>
-      <c r="M128" s="1" t="inlineStr"/>
-      <c r="N128" s="1" t="inlineStr"/>
-      <c r="O128" s="1" t="inlineStr"/>
-      <c r="P128" s="1" t="inlineStr"/>
-      <c r="Q128" s="1" t="inlineStr"/>
-      <c r="R128" s="1" t="inlineStr"/>
-      <c r="S128" s="1" t="inlineStr"/>
-      <c r="T128" s="1" t="inlineStr"/>
-      <c r="U128" s="1" t="inlineStr"/>
-      <c r="V128" s="1" t="inlineStr"/>
-      <c r="W128" s="1" t="inlineStr"/>
-      <c r="X128" s="1" t="inlineStr"/>
-      <c r="Y128" s="1" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="inlineStr"/>
-      <c r="B129" s="1" t="inlineStr"/>
-      <c r="C129" s="1" t="inlineStr"/>
-      <c r="D129" s="1" t="inlineStr"/>
-      <c r="E129" s="1" t="inlineStr"/>
-      <c r="F129" s="1" t="inlineStr"/>
-      <c r="G129" s="1" t="inlineStr"/>
-      <c r="H129" s="1" t="inlineStr"/>
-      <c r="I129" s="1" t="inlineStr"/>
-      <c r="J129" s="1" t="inlineStr"/>
-      <c r="K129" s="1" t="inlineStr">
-        <is>
-          <t>L2394: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: full of womenâ€”two thousand of all classes, it</t>
-        </is>
-      </c>
-      <c r="L129" s="1" t="inlineStr"/>
-      <c r="M129" s="1" t="inlineStr"/>
-      <c r="N129" s="1" t="inlineStr"/>
-      <c r="O129" s="1" t="inlineStr"/>
-      <c r="P129" s="1" t="inlineStr"/>
-      <c r="Q129" s="1" t="inlineStr"/>
-      <c r="R129" s="1" t="inlineStr"/>
-      <c r="S129" s="1" t="inlineStr"/>
-      <c r="T129" s="1" t="inlineStr"/>
-      <c r="U129" s="1" t="inlineStr"/>
-      <c r="V129" s="1" t="inlineStr"/>
-      <c r="W129" s="1" t="inlineStr"/>
-      <c r="X129" s="1" t="inlineStr"/>
-      <c r="Y129" s="1" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="inlineStr"/>
-      <c r="B130" s="1" t="inlineStr"/>
-      <c r="C130" s="1" t="inlineStr"/>
-      <c r="D130" s="1" t="inlineStr"/>
-      <c r="E130" s="1" t="inlineStr"/>
-      <c r="F130" s="1" t="inlineStr"/>
-      <c r="G130" s="1" t="inlineStr"/>
-      <c r="H130" s="1" t="inlineStr"/>
-      <c r="I130" s="1" t="inlineStr"/>
-      <c r="J130" s="1" t="inlineStr"/>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>L2431: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜' from the best English pedigrees.</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr"/>
-      <c r="M130" s="1" t="inlineStr"/>
-      <c r="N130" s="1" t="inlineStr"/>
-      <c r="O130" s="1" t="inlineStr"/>
-      <c r="P130" s="1" t="inlineStr"/>
-      <c r="Q130" s="1" t="inlineStr"/>
-      <c r="R130" s="1" t="inlineStr"/>
-      <c r="S130" s="1" t="inlineStr"/>
-      <c r="T130" s="1" t="inlineStr"/>
-      <c r="U130" s="1" t="inlineStr"/>
-      <c r="V130" s="1" t="inlineStr"/>
-      <c r="W130" s="1" t="inlineStr"/>
-      <c r="X130" s="1" t="inlineStr"/>
-      <c r="Y130" s="1" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr"/>
-      <c r="B131" s="1" t="inlineStr"/>
-      <c r="C131" s="1" t="inlineStr"/>
-      <c r="D131" s="1" t="inlineStr"/>
-      <c r="E131" s="1" t="inlineStr"/>
-      <c r="F131" s="1" t="inlineStr"/>
-      <c r="G131" s="1" t="inlineStr"/>
-      <c r="H131" s="1" t="inlineStr"/>
-      <c r="I131" s="1" t="inlineStr"/>
-      <c r="J131" s="1" t="inlineStr"/>
-      <c r="K131" s="1" t="inlineStr">
-        <is>
-          <t>L2437: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: Â¥</t>
-        </is>
-      </c>
-      <c r="L131" s="1" t="inlineStr"/>
-      <c r="M131" s="1" t="inlineStr"/>
-      <c r="N131" s="1" t="inlineStr"/>
-      <c r="O131" s="1" t="inlineStr"/>
-      <c r="P131" s="1" t="inlineStr"/>
-      <c r="Q131" s="1" t="inlineStr"/>
-      <c r="R131" s="1" t="inlineStr"/>
-      <c r="S131" s="1" t="inlineStr"/>
-      <c r="T131" s="1" t="inlineStr"/>
-      <c r="U131" s="1" t="inlineStr"/>
-      <c r="V131" s="1" t="inlineStr"/>
-      <c r="W131" s="1" t="inlineStr"/>
-      <c r="X131" s="1" t="inlineStr"/>
-      <c r="Y131" s="1" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="inlineStr"/>
-      <c r="B132" s="1" t="inlineStr"/>
-      <c r="C132" s="1" t="inlineStr"/>
-      <c r="D132" s="1" t="inlineStr"/>
-      <c r="E132" s="1" t="inlineStr"/>
-      <c r="F132" s="1" t="inlineStr"/>
-      <c r="G132" s="1" t="inlineStr"/>
-      <c r="H132" s="1" t="inlineStr"/>
-      <c r="I132" s="1" t="inlineStr"/>
-      <c r="J132" s="1" t="inlineStr"/>
-      <c r="K132" s="1" t="inlineStr">
-        <is>
-          <t>L2439: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L132" s="1" t="inlineStr"/>
-      <c r="M132" s="1" t="inlineStr"/>
-      <c r="N132" s="1" t="inlineStr"/>
-      <c r="O132" s="1" t="inlineStr"/>
-      <c r="P132" s="1" t="inlineStr"/>
-      <c r="Q132" s="1" t="inlineStr"/>
-      <c r="R132" s="1" t="inlineStr"/>
-      <c r="S132" s="1" t="inlineStr"/>
-      <c r="T132" s="1" t="inlineStr"/>
-      <c r="U132" s="1" t="inlineStr"/>
-      <c r="V132" s="1" t="inlineStr"/>
-      <c r="W132" s="1" t="inlineStr"/>
-      <c r="X132" s="1" t="inlineStr"/>
-      <c r="Y132" s="1" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr"/>
-      <c r="B133" s="1" t="inlineStr"/>
-      <c r="C133" s="1" t="inlineStr"/>
-      <c r="D133" s="1" t="inlineStr"/>
-      <c r="E133" s="1" t="inlineStr"/>
-      <c r="F133" s="1" t="inlineStr"/>
-      <c r="G133" s="1" t="inlineStr"/>
-      <c r="H133" s="1" t="inlineStr"/>
-      <c r="I133" s="1" t="inlineStr"/>
-      <c r="J133" s="1" t="inlineStr"/>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>L2443: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr"/>
-      <c r="M133" s="1" t="inlineStr"/>
-      <c r="N133" s="1" t="inlineStr"/>
-      <c r="O133" s="1" t="inlineStr"/>
-      <c r="P133" s="1" t="inlineStr"/>
-      <c r="Q133" s="1" t="inlineStr"/>
-      <c r="R133" s="1" t="inlineStr"/>
-      <c r="S133" s="1" t="inlineStr"/>
-      <c r="T133" s="1" t="inlineStr"/>
-      <c r="U133" s="1" t="inlineStr"/>
-      <c r="V133" s="1" t="inlineStr"/>
-      <c r="W133" s="1" t="inlineStr"/>
-      <c r="X133" s="1" t="inlineStr"/>
-      <c r="Y133" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
